--- a/Business - Technology Services/Datacenter/CRWV.xlsx
+++ b/Business - Technology Services/Datacenter/CRWV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\models\Business - Technology Services\Datacenter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6701F33B-CBC8-4E1B-95B7-8B0F477A2ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F44DECD-C813-4EAD-AD7A-DFC9C608DBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,16 @@
     <sheet name="DoR" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Model!$B$25</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Model!$B$26</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Model!$K$25:$X$25</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Model!$K$26:$X$26</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Model!$K$2:$T$2</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Model!$B$6</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Model!$B$7</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Model!$K$2:$T$2</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Model!$K$6:$X$6</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Model!$K$7:$X$7</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Model!$B$6</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Model!$B$7</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Model!$K$2:$P$2</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Model!$K$6:$T$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Model!$K$7:$T$7</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Model!$B$23</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Model!$B$24</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Model!$K$23:$T$23</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Model!$K$24:$T$24</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Model!$K$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -319,7 +319,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="199">
   <si>
     <t>Price</t>
   </si>
@@ -337,12 +337,6 @@
   </si>
   <si>
     <t>EV</t>
-  </si>
-  <si>
-    <t>Q123</t>
-  </si>
-  <si>
-    <t>FY22</t>
   </si>
   <si>
     <t>FY23</t>
@@ -366,9 +360,6 @@
     <t>Operational Income</t>
   </si>
   <si>
-    <t>D&amp;A</t>
-  </si>
-  <si>
     <t>Cash</t>
   </si>
   <si>
@@ -379,9 +370,6 @@
   </si>
   <si>
     <t>Goodwill</t>
-  </si>
-  <si>
-    <t>Other long-term liabilieties</t>
   </si>
   <si>
     <t>Total Assets</t>
@@ -402,9 +390,6 @@
     <t>FY24</t>
   </si>
   <si>
-    <t>Q223</t>
-  </si>
-  <si>
     <t>Net CASH</t>
   </si>
   <si>
@@ -412,12 +397,6 @@
   </si>
   <si>
     <t>Net Cash</t>
-  </si>
-  <si>
-    <t>Q323</t>
-  </si>
-  <si>
-    <t>Q423</t>
   </si>
   <si>
     <t>Last Update</t>
@@ -477,16 +456,10 @@
     <t>COGS</t>
   </si>
   <si>
-    <t>Sales &amp; Marketing</t>
-  </si>
-  <si>
     <t>Current Assets</t>
   </si>
   <si>
     <t>Total Current Liabilities</t>
-  </si>
-  <si>
-    <t>Gains on Equity</t>
   </si>
   <si>
     <t>Operating Lease</t>
@@ -501,13 +474,7 @@
     <t>Rev. Exp.</t>
   </si>
   <si>
-    <t>Sales &amp; Marketing / REV</t>
-  </si>
-  <si>
     <t>Q224</t>
-  </si>
-  <si>
-    <t>Interest Collect (exp)</t>
   </si>
   <si>
     <t>FY25</t>
@@ -525,19 +492,10 @@
     <t>EV/EBITDA</t>
   </si>
   <si>
-    <t>R&amp;D</t>
-  </si>
-  <si>
-    <t>NI Noncontrolling Interest</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>Restricted Cash</t>
-  </si>
-  <si>
-    <t>Receivables</t>
   </si>
   <si>
     <t>Prepaid Expense</t>
@@ -552,37 +510,7 @@
     <t>Intangible Asset</t>
   </si>
   <si>
-    <t>Deffered Income Tax</t>
-  </si>
-  <si>
-    <t>Long term debt</t>
-  </si>
-  <si>
-    <t>Acctured Liab</t>
-  </si>
-  <si>
     <t>Equity</t>
-  </si>
-  <si>
-    <t>Rights of use</t>
-  </si>
-  <si>
-    <t>Current position in LTB</t>
-  </si>
-  <si>
-    <t>Interest exp / REV</t>
-  </si>
-  <si>
-    <t>Interest exp / op Inc</t>
-  </si>
-  <si>
-    <t>Assets of Businesses for Sale</t>
-  </si>
-  <si>
-    <t>Liab Business for Sale</t>
-  </si>
-  <si>
-    <t>Inventories</t>
   </si>
   <si>
     <t>Interest Rate debt</t>
@@ -768,9 +696,6 @@
     <t>Prod2 y/y</t>
   </si>
   <si>
-    <t>R&amp;D / REV</t>
-  </si>
-  <si>
     <t>G&amp;A / REV</t>
   </si>
   <si>
@@ -835,6 +760,162 @@
   </si>
   <si>
     <t>Q226</t>
+  </si>
+  <si>
+    <t>$CRWV</t>
+  </si>
+  <si>
+    <t>CoreWeave, Inc. operates a cloud platform that provides scaling, support, and acceleration for GenAI. The company builds the infrastructure that supports compute workloads for enterprises. Its products include GPU compute, CPU compute, storage services, networking services, managed services, and virtual and bare metal servers. Additionally, its platform offers a fleet lifecycle controller, node lifecycle controller, tensorizer, and observability. The company's services also include VFX and rendering, AI model training, AI interference, and mission control. CoreWeave, Inc. was formerly known as Atlantic Crypto Corporation and changed its name to CoreWeave, Inc. in December 2019. CoreWeave, Inc. was incorporated in 2017 and is based in Livingston, New Jersey</t>
+  </si>
+  <si>
+    <t>Michael N. Intrator</t>
+  </si>
+  <si>
+    <t>Co-Founder, CEO</t>
+  </si>
+  <si>
+    <t>Brannin McBee</t>
+  </si>
+  <si>
+    <t>Co-Founder, Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Co-Founder, CSO</t>
+  </si>
+  <si>
+    <t>Brian Venturo</t>
+  </si>
+  <si>
+    <t>Nitin Agrawal</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>Ernie Rogers</t>
+  </si>
+  <si>
+    <t>Stategic Financing</t>
+  </si>
+  <si>
+    <t>Jon Jones</t>
+  </si>
+  <si>
+    <t>Revenue Officer</t>
+  </si>
+  <si>
+    <t>Peter Salanski</t>
+  </si>
+  <si>
+    <t>Co-Founder, CTO</t>
+  </si>
+  <si>
+    <t>Sachin Jin</t>
+  </si>
+  <si>
+    <t>COO</t>
+  </si>
+  <si>
+    <t>Magnetar Financial</t>
+  </si>
+  <si>
+    <t>Vanguard</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>Goldman</t>
+  </si>
+  <si>
+    <t>FMR</t>
+  </si>
+  <si>
+    <t>Blackrock</t>
+  </si>
+  <si>
+    <t>Jane Street</t>
+  </si>
+  <si>
+    <t>Situational Awareness</t>
+  </si>
+  <si>
+    <t>Value Aligned Research</t>
+  </si>
+  <si>
+    <t>Peak6 LLC</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Restricted MS</t>
+  </si>
+  <si>
+    <t>Other non-current</t>
+  </si>
+  <si>
+    <t>Accrued Liab</t>
+  </si>
+  <si>
+    <t>Debt current</t>
+  </si>
+  <si>
+    <t>Finance lease</t>
+  </si>
+  <si>
+    <t>Other current liab</t>
+  </si>
+  <si>
+    <t>Debt</t>
+  </si>
+  <si>
+    <t>Derivative and warrant liab</t>
+  </si>
+  <si>
+    <t>Operating lease</t>
+  </si>
+  <si>
+    <t>Finance lase</t>
+  </si>
+  <si>
+    <t>Deferred Tax</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Deferred Revenue</t>
+  </si>
+  <si>
+    <t>FY27</t>
+  </si>
+  <si>
+    <t>Tech &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t>S&amp;M</t>
+  </si>
+  <si>
+    <t>Gain/loss on fair value adj</t>
+  </si>
+  <si>
+    <t>Interest expense net</t>
+  </si>
+  <si>
+    <t>Shares (diluted)</t>
+  </si>
+  <si>
+    <t>Tech Infra / REV</t>
+  </si>
+  <si>
+    <t>S&amp;M / REV</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -955,7 +1036,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -989,12 +1070,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9B9B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1582,9 +1657,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1613,9 +1688,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1634,11 +1706,8 @@
     <xf numFmtId="3" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1655,84 +1724,84 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="12" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="12" fillId="11" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="12" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="12" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="41" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="11" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="14" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="10" fillId="9" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="10" fillId="9" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="29" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="9" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="10" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1740,52 +1809,52 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1797,6 +1866,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3708,7 +3792,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dPt>
-            <c:idx val="11"/>
+            <c:idx val="7"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -3720,14 +3804,9 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-E309-400E-9279-09DE67BBD1C5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
-            <c:idx val="12"/>
+            <c:idx val="8"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -3741,11 +3820,6 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E309-400E-9279-09DE67BBD1C5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3804,49 +3878,37 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Model!$K$2:$X$2</c:f>
+              <c:f>Model!$K$2:$T$2</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>Q123</c:v>
+                  <c:v>Q124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Q223</c:v>
+                  <c:v>Q224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Q323</c:v>
+                  <c:v>Q324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Q423</c:v>
+                  <c:v>Q424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Q124</c:v>
+                  <c:v>Q125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Q224</c:v>
+                  <c:v>Q225</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Q324</c:v>
+                  <c:v>Q325</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Q424</c:v>
+                  <c:v>Q425</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Q125</c:v>
+                  <c:v>Q126</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Q225</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Q325</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Q425</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Q126</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>Q226</c:v>
                 </c:pt>
               </c:strCache>
@@ -3854,50 +3916,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$6:$X$6</c:f>
+              <c:f>Model!$K$6:$T$6</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>188.684</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>395.37099999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>583.94100000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>747.00400000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>981.63199999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1212.788</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1364.6759999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1571.904</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -3930,7 +3980,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$29</c:f>
+              <c:f>Model!$B$27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4007,39 +4057,27 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$29:$X$29</c:f>
+              <c:f>Model!$K$27:$T$27</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4.2025184965338873</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2.0674682766313159</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.3370100746479521</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.1042778887395515</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4500,19 +4538,19 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>FY22</c:v>
+                  <c:v>FY23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FY23</c:v>
+                  <c:v>FY24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>FY24</c:v>
+                  <c:v>FY25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FY25</c:v>
+                  <c:v>FY26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>FY26</c:v>
+                  <c:v>FY27</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4524,13 +4562,13 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>229</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1915</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5131</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4567,7 +4605,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$29</c:f>
+              <c:f>Model!$B$27</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4654,18 +4692,18 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$29:$G$29</c:f>
+              <c:f>Model!$C$27:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>7.3624454148471621</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1.679373368146214</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -5012,7 +5050,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$25</c:f>
+              <c:f>Model!$B$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5088,37 +5126,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Model!$K$2:$T$2</c:f>
+              <c:f>Model!$K$2:$P$2</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Q123</c:v>
+                  <c:v>Q124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Q223</c:v>
+                  <c:v>Q224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Q323</c:v>
+                  <c:v>Q324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Q423</c:v>
+                  <c:v>Q424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Q124</c:v>
+                  <c:v>Q125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Q224</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Q324</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Q424</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Q125</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Q225</c:v>
                 </c:pt>
               </c:strCache>
@@ -5126,50 +5152,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$25:$X$25</c:f>
+              <c:f>Model!$K$23:$T$23</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-0.61773758770336673</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-1.5409395781057695</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-1.6828667109435653</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>-0.23817853568188027</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>-1.2621333130091905</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>-0.59702912713140999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>-0.22118316241067248</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>-0.90728801372201595</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5202,7 +5216,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$35</c:f>
+              <c:f>Model!$B$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5279,39 +5293,27 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$35:$X$35</c:f>
+              <c:f>Model!$K$33:$T$33</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.4343974374845265</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>-0.10064980295398807</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>-0.69393591564366419</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>7.8705914696410098</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5655,7 +5657,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$25</c:f>
+              <c:f>Model!$B$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5733,37 +5735,37 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>FY22</c:v>
+                  <c:v>FY23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FY23</c:v>
+                  <c:v>FY24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>FY24</c:v>
+                  <c:v>FY25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FY25</c:v>
+                  <c:v>FY26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>FY26</c:v>
+                  <c:v>FY27</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$25:$G$25</c:f>
+              <c:f>Model!$C$23:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-3.09375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-3.9587155963302751</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-2.676605504587156</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -5801,7 +5803,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$35</c:f>
+              <c:f>Model!$B$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5876,7 +5878,7 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$35:$G$35</c:f>
+              <c:f>Model!$C$33:$G$33</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -5884,10 +5886,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.27958483921786681</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-0.32387022016222478</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -6252,11 +6254,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$30</c:f>
+              <c:f>Model!$B$28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Sales &amp; Marketing / REV</c:v>
+                  <c:v>Tech Infra / REV</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6345,37 +6347,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Model!$K$2:$T$2</c:f>
+              <c:f>Model!$K$2:$P$2</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Q123</c:v>
+                  <c:v>Q124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Q223</c:v>
+                  <c:v>Q224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Q323</c:v>
+                  <c:v>Q324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Q423</c:v>
+                  <c:v>Q424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Q124</c:v>
+                  <c:v>Q125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Q224</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Q324</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Q424</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Q125</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Q225</c:v>
                 </c:pt>
               </c:strCache>
@@ -6383,50 +6373,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$30:$X$30</c:f>
+              <c:f>Model!$K$28:$T$28</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.49225689512624282</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.46256806897825081</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.48893466976971989</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.53510289101530917</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.57190678380492899</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.55237436386243932</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.54773367451321786</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.60449365864582039</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6444,11 +6422,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$31</c:f>
+              <c:f>Model!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>R&amp;D / REV</c:v>
+                  <c:v>S&amp;M / REV</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6537,37 +6515,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Model!$K$2:$T$2</c:f>
+              <c:f>Model!$K$2:$P$2</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Q123</c:v>
+                  <c:v>Q124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Q223</c:v>
+                  <c:v>Q224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Q323</c:v>
+                  <c:v>Q324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Q423</c:v>
+                  <c:v>Q424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Q124</c:v>
+                  <c:v>Q125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Q224</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Q324</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Q424</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Q125</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Q225</c:v>
                 </c:pt>
               </c:strCache>
@@ -6575,50 +6541,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$31:$X$31</c:f>
+              <c:f>Model!$K$29:$T$29</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.146445909563079E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.0552114343237112E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>7.7987330911855821E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>6.9932691123474585E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.0746389685747816E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.0342483599771763E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>3.2714724960356892E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>3.3085353812955492E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -6636,7 +6590,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$32</c:f>
+              <c:f>Model!$B$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6729,37 +6683,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Model!$K$2:$T$2</c:f>
+              <c:f>Model!$K$2:$P$2</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Q123</c:v>
+                  <c:v>Q124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Q223</c:v>
+                  <c:v>Q224</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Q323</c:v>
+                  <c:v>Q324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Q423</c:v>
+                  <c:v>Q424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Q124</c:v>
+                  <c:v>Q125</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Q224</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Q324</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Q424</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Q125</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>Q225</c:v>
                 </c:pt>
               </c:strCache>
@@ -6767,50 +6709,38 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$K$32:$X$32</c:f>
+              <c:f>Model!$K$30:$T$30</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>8.3133705030633234E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>5.502173907545066E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5.7588009747560114E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>6.4165653731439176E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.17802699993480248</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.1436359858441871</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.11129235071181731</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>9.5530643092707965E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7117,11 +7047,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$30</c:f>
+              <c:f>Model!$B$28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Sales &amp; Marketing / REV</c:v>
+                  <c:v>Tech Infra / REV</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7214,37 +7144,37 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>FY22</c:v>
+                  <c:v>FY23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FY23</c:v>
+                  <c:v>FY24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>FY24</c:v>
+                  <c:v>FY25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FY25</c:v>
+                  <c:v>FY26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>FY26</c:v>
+                  <c:v>FY27</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$30:$G$30</c:f>
+              <c:f>Model!$C$28:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.57205240174672489</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.50182767624020885</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.57084389007990644</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -7267,11 +7197,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$31</c:f>
+              <c:f>Model!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>R&amp;D / REV</c:v>
+                  <c:v>S&amp;M / REV</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7364,37 +7294,37 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>FY22</c:v>
+                  <c:v>FY23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FY23</c:v>
+                  <c:v>FY24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>FY24</c:v>
+                  <c:v>FY25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FY25</c:v>
+                  <c:v>FY26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>FY26</c:v>
+                  <c:v>FY27</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$31:$F$31</c:f>
+              <c:f>Model!$C$29:$F$29</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5.6768558951965066E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.3994778067885126E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.8064704735918926E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -7414,7 +7344,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Model!$B$32</c:f>
+              <c:f>Model!$B$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7511,37 +7441,37 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>FY22</c:v>
+                  <c:v>FY23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FY23</c:v>
+                  <c:v>FY24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>FY24</c:v>
+                  <c:v>FY25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>FY25</c:v>
+                  <c:v>FY26</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>FY26</c:v>
+                  <c:v>FY27</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Model!$C$32:$F$32</c:f>
+              <c:f>Model!$C$30:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.13100436681222707</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>6.2140992167101824E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.12687585266030013</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -8067,18 +7997,18 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f dir="row">_xlchart.v1.4</cx:f>
+        <cx:f dir="row">_xlchart.v1.9</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.3</cx:f>
+        <cx:f dir="row">_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
-        <cx:f dir="row">_xlchart.v1.4</cx:f>
+        <cx:f dir="row">_xlchart.v1.9</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.2</cx:f>
+        <cx:f dir="row">_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -8122,7 +8052,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{006F4749-938E-4621-8334-C74E7B83CC40}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>EPS exp.</cx:v>
             </cx:txData>
           </cx:tx>
@@ -8142,7 +8072,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{C8A70830-D21B-405F-8F13-72F0AC678416}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:f>_xlchart.v1.5</cx:f>
               <cx:v>EPS</cx:v>
             </cx:txData>
           </cx:tx>
@@ -8173,18 +8103,18 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f dir="row">_xlchart.v1.7</cx:f>
+        <cx:f dir="row">_xlchart.v1.2</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.9</cx:f>
+        <cx:f dir="row">_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
-        <cx:f dir="row">_xlchart.v1.7</cx:f>
+        <cx:f dir="row">_xlchart.v1.2</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.8</cx:f>
+        <cx:f dir="row">_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -8228,7 +8158,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{006F4749-938E-4621-8334-C74E7B83CC40}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.6</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Rev. Exp.</cx:v>
             </cx:txData>
           </cx:tx>
@@ -8248,7 +8178,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{C8A70830-D21B-405F-8F13-72F0AC678416}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.5</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Revenue</cx:v>
             </cx:txData>
           </cx:tx>
@@ -15384,6 +15314,55 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEDDD6AB-5957-993D-170B-289A7320BEE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="190500" y="390525"/>
+          <a:ext cx="6715125" cy="1550837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -15425,7 +15404,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -15749,92 +15728,144 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="34"/>
+      <c r="B2" s="33" t="s">
+        <v>147</v>
+      </c>
       <c r="C2" s="19"/>
       <c r="E2" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="26" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>49</v>
+      <c r="L2" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="20">
-        <v>45971</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="28"/>
+        <v>46148</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="140">
+        <v>0.15390000000000001</v>
+      </c>
       <c r="I3" s="10"/>
-      <c r="J3" s="38"/>
-      <c r="L3" s="5"/>
-      <c r="N3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="L3" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="M3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="36"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="5"/>
       <c r="C4" s="21">
-        <v>0.60555555555555551</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="28"/>
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="140">
+        <v>6.3E-2</v>
+      </c>
       <c r="I4" s="10"/>
-      <c r="J4" s="38"/>
-      <c r="L4" s="5"/>
+      <c r="J4" s="37"/>
+      <c r="L4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M4" t="s">
+        <v>152</v>
+      </c>
       <c r="N4" s="13"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
       <c r="C5" s="13"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="28"/>
+      <c r="E5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="140">
+        <v>5.4800000000000001E-2</v>
+      </c>
       <c r="I5" s="10"/>
-      <c r="J5" s="38"/>
-      <c r="L5" s="5"/>
+      <c r="J5" s="37"/>
+      <c r="L5" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="M5" t="s">
+        <v>153</v>
+      </c>
       <c r="N5" s="13"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="28"/>
+      <c r="C6" s="13">
+        <v>134</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F6" s="140">
+        <v>2.0500000000000001E-2</v>
+      </c>
       <c r="I6" s="10"/>
-      <c r="J6" s="38"/>
-      <c r="L6" s="5"/>
+      <c r="J6" s="37"/>
+      <c r="L6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="M6" t="s">
+        <v>156</v>
+      </c>
       <c r="N6" s="13"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="28"/>
+      <c r="C7" s="15">
+        <f>Model!R22</f>
+        <v>497.88600000000002</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="140">
+        <v>1.7899999999999999E-2</v>
+      </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="38"/>
-      <c r="L7" s="5"/>
+      <c r="J7" s="37"/>
+      <c r="L7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M7" t="s">
+        <v>158</v>
+      </c>
       <c r="N7" s="13"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -15843,28 +15874,46 @@
       </c>
       <c r="C8" s="15">
         <f>C6*C7</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="28"/>
+        <v>66716.724000000002</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="140">
+        <v>1.6299999999999999E-2</v>
+      </c>
       <c r="I8" s="10"/>
-      <c r="J8" s="38"/>
-      <c r="L8" s="5"/>
+      <c r="J8" s="37"/>
+      <c r="L8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="M8" t="s">
+        <v>160</v>
+      </c>
       <c r="N8" s="13"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="15" t="e">
-        <f>Model!C28</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="28"/>
+      <c r="C9" s="15">
+        <f>Model!R37</f>
+        <v>3127</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="140">
+        <v>1.3899999999999999E-2</v>
+      </c>
       <c r="I9" s="10"/>
-      <c r="J9" s="38"/>
-      <c r="L9" s="5"/>
+      <c r="J9" s="37"/>
+      <c r="L9" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="M9" t="s">
+        <v>162</v>
+      </c>
       <c r="N9" s="13"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -15872,28 +15921,41 @@
         <v>4</v>
       </c>
       <c r="C10" s="15">
-        <f>Model!C41+Model!C45</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="28"/>
+        <f>Model!R53+Model!R59</f>
+        <v>21373</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="140">
+        <v>1.38E-2</v>
+      </c>
       <c r="I10" s="10"/>
-      <c r="J10" s="38"/>
-      <c r="L10" s="5"/>
+      <c r="J10" s="37"/>
+      <c r="L10" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="M10" t="s">
+        <v>164</v>
+      </c>
       <c r="N10" s="13"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="15" t="e">
+        <v>23</v>
+      </c>
+      <c r="C11" s="15">
         <f>C9-C10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="28"/>
+        <v>-18246</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="140">
+        <v>1.3599999999999999E-2</v>
+      </c>
       <c r="I11" s="10"/>
-      <c r="J11" s="38"/>
+      <c r="J11" s="37"/>
       <c r="L11" s="5"/>
       <c r="N11" s="13"/>
     </row>
@@ -15901,23 +15963,27 @@
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="15" t="e">
+      <c r="C12" s="15">
         <f>C8-C9+C10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="28"/>
+        <v>84962.724000000002</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="140">
+        <v>1.3100000000000001E-2</v>
+      </c>
       <c r="J12" s="13"/>
       <c r="L12" s="5"/>
       <c r="N12" s="13"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="36" t="e">
-        <f>C6/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>32</v>
+      </c>
+      <c r="C13" s="35">
+        <f>C6/Model!E23</f>
+        <v>-50.063410454155957</v>
       </c>
       <c r="E13" s="5"/>
       <c r="J13" s="13"/>
@@ -15926,350 +15992,344 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="36" t="e">
-        <f>C6/Model!D16</f>
-        <v>#DIV/0!</v>
+        <v>30</v>
+      </c>
+      <c r="C14" s="35">
+        <f>C6/Model!F24</f>
+        <v>-49.446494464944649</v>
       </c>
       <c r="E14" s="22"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
       <c r="J14" s="23"/>
       <c r="L14" s="22"/>
-      <c r="M14" s="29"/>
+      <c r="M14" s="28"/>
       <c r="N14" s="23"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="36" t="e">
-        <f>C6/Model!E16</f>
-        <v>#DIV/0!</v>
+        <v>31</v>
+      </c>
+      <c r="C15" s="35">
+        <f>Main!C6/Model!G24</f>
+        <v>-297.77777777777777</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="6" t="e">
-        <f>Model!D16/Model!#REF!-1</f>
-        <v>#REF!</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="6" t="e">
-        <f>Model!E16/Model!D16-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" s="125"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="127"/>
+        <v>29</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="L17" s="121" t="s">
+        <v>148</v>
+      </c>
+      <c r="M17" s="122"/>
+      <c r="N17" s="123"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="46" t="e">
+        <v>53</v>
+      </c>
+      <c r="C18" s="45">
         <f>C14/(C16*100)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L18" s="128"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="130"/>
+        <v>-9.8892988929889292</v>
+      </c>
+      <c r="L18" s="124"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="126"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="46" t="e">
+        <v>54</v>
+      </c>
+      <c r="C19" s="45">
         <f>C15/(C17*100)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L19" s="128"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="130"/>
+        <v>-3.7222222222222223</v>
+      </c>
+      <c r="L19" s="124"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="126"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="6" t="e">
-        <f>Model!D4/Model!C3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L20" s="128"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="130"/>
+        <v>65</v>
+      </c>
+      <c r="C20" s="6">
+        <f>Model!F7/Model!E6-1</f>
+        <v>1.4400701617618399</v>
+      </c>
+      <c r="L20" s="124"/>
+      <c r="M20" s="125"/>
+      <c r="N20" s="126"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="6" t="e">
-        <f>Model!D5/Model!C4-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="128"/>
-      <c r="M21" s="129"/>
-      <c r="N21" s="130"/>
+        <v>66</v>
+      </c>
+      <c r="C21" s="6">
+        <f>Model!G7/Model!F7-1</f>
+        <v>0.89696485623003186</v>
+      </c>
+      <c r="L21" s="124"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="126"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C22" s="15">
-        <f>Model!C12+Model!C10</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="128"/>
-      <c r="M22" s="129"/>
-      <c r="N22" s="130"/>
+        <f>Model!E19</f>
+        <v>-1215</v>
+      </c>
+      <c r="L22" s="124"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="126"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" s="15">
-        <f>Model!C12</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="128"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="130"/>
+        <f>Model!E19</f>
+        <v>-1215</v>
+      </c>
+      <c r="L23" s="124"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="126"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" s="7">
-        <f>Model!C17</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="128"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="130"/>
+        <f>Model!E25</f>
+        <v>0.71681933346326254</v>
+      </c>
+      <c r="L24" s="124"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="126"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C25" s="7">
-        <f>Model!C18</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="128"/>
-      <c r="M25" s="129"/>
-      <c r="N25" s="130"/>
+        <f>Model!E26</f>
+        <v>-0.22744104463067627</v>
+      </c>
+      <c r="L25" s="124"/>
+      <c r="M25" s="125"/>
+      <c r="N25" s="126"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="36" t="e">
+        <v>56</v>
+      </c>
+      <c r="C26" s="35">
         <f>C12/C23</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L26" s="128"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="130"/>
+        <v>-69.928167901234573</v>
+      </c>
+      <c r="L26" s="124"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="126"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="115" t="e">
-        <f>Model!#REF!/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>67</v>
+      </c>
+      <c r="C27" s="111">
+        <f>Main!C10/Model!R67</f>
+        <v>-4.3727516582719028</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
-      </c>
-      <c r="L27" s="128"/>
-      <c r="M27" s="129"/>
-      <c r="N27" s="130"/>
+        <v>57</v>
+      </c>
+      <c r="L27" s="124"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="126"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="36" t="e">
-        <f>C22/-Model!C10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L28" s="131"/>
-      <c r="M28" s="132"/>
-      <c r="N28" s="133"/>
+        <v>68</v>
+      </c>
+      <c r="C28" s="35">
+        <f>Model!E19/Model!E17</f>
+        <v>0.98860862489829127</v>
+      </c>
+      <c r="L28" s="127"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="129"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="36" t="e">
-        <f>Model!#REF!/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>69</v>
+      </c>
+      <c r="C29" s="35">
+        <f>Model!E42/Model!E50</f>
+        <v>0.18228189325160443</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="36" t="e">
-        <f>(Model!#REF!+Model!#REF!)/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>70</v>
+      </c>
+      <c r="C30" s="35">
+        <f>(Model!E37+Model!E39)/Model!E51</f>
+        <v>1.9476278496611215</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="6" t="e">
-        <f>(Model!#REF!-Model!#REF!)/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>71</v>
+      </c>
+      <c r="C31" s="6">
+        <f>(Model!E42-Model!E58)/Model!E50</f>
+        <v>-0.2179203403296425</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="36" t="e">
-        <f>(Model!#REF!-Model!#REF!)/Main!C7</f>
-        <v>#REF!</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C32" s="35"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="36" t="e">
-        <f>Model!#REF!/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>73</v>
+      </c>
+      <c r="C33" s="35">
+        <f>Model!E6/Model!E50</f>
+        <v>0.12490496718402543</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="38" t="e">
-        <f>Model!#REF!/Model!#REF!</f>
-        <v>#REF!</v>
+        <v>74</v>
+      </c>
+      <c r="C34" s="37">
+        <f>Model!E21/Model!E50</f>
+        <v>-2.8408516215895085E-2</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="38" t="e">
-        <f>Model!#REF!/Model!#REF!</f>
-        <v>#REF!</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C35" s="37"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C36" s="23"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="50"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="54"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="54"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="54"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="50"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="54"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="50"/>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E47" s="51"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="50"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="54"/>
-      <c r="H48" s="54"/>
-      <c r="I48" s="54"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
     </row>
     <row r="49" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="50"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="50"/>
     </row>
     <row r="50" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="50"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="50"/>
     </row>
     <row r="51" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="54"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="50"/>
+      <c r="I51" s="50"/>
     </row>
     <row r="52" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E52" s="52"/>
-      <c r="F52" s="53"/>
-      <c r="G52" s="53"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
     </row>
     <row r="53" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E53" s="52"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="53"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
     </row>
     <row r="54" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E54" s="52"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16282,111 +16342,141 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7345E9-1C5F-45F5-BD7C-66FA029FFFF4}">
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:Z88"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="13"/>
-    <col min="21" max="21" width="11.42578125" style="13"/>
+    <col min="17" max="17" width="11.42578125" style="144"/>
+    <col min="19" max="19" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q2" s="144" t="s">
+        <v>143</v>
+      </c>
+      <c r="R2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="T2" t="s">
+        <v>146</v>
+      </c>
+      <c r="U2" t="s">
+        <v>197</v>
+      </c>
+      <c r="V2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>229</v>
+      </c>
+      <c r="D3">
+        <v>1915</v>
+      </c>
+      <c r="E3" s="13">
+        <v>5131</v>
+      </c>
+      <c r="K3">
+        <v>188.684</v>
+      </c>
+      <c r="L3">
+        <v>395.37099999999998</v>
+      </c>
+      <c r="M3">
+        <v>583.94100000000003</v>
+      </c>
+      <c r="N3">
+        <f>D3-M3-L3-K3</f>
+        <v>747.00400000000002</v>
+      </c>
+      <c r="O3">
+        <v>981.63199999999995</v>
+      </c>
+      <c r="P3">
+        <v>1212.788</v>
+      </c>
+      <c r="Q3" s="144">
+        <v>1364.6759999999999</v>
+      </c>
+      <c r="R3">
+        <f>E3-Q3-P3-O3</f>
+        <v>1571.904</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+    </row>
+    <row r="6" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>57</v>
-      </c>
-      <c r="P2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>153</v>
-      </c>
-      <c r="R2" t="s">
-        <v>154</v>
-      </c>
-      <c r="S2" t="s">
-        <v>166</v>
-      </c>
-      <c r="T2" t="s">
-        <v>167</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="V2" t="s">
-        <v>169</v>
-      </c>
-      <c r="W2" t="s">
-        <v>170</v>
-      </c>
-      <c r="X2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-    </row>
-    <row r="6" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C6" s="11">
         <f>SUM(C3:C5)</f>
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="D6" s="11">
         <f>SUM(D3:D5)</f>
-        <v>0</v>
+        <v>1915</v>
       </c>
       <c r="E6" s="14">
         <f t="shared" ref="E6:G6" si="0">SUM(E3:E5)</f>
-        <v>0</v>
+        <v>5131</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" si="0"/>
@@ -16398,37 +16488,37 @@
       </c>
       <c r="K6" s="11">
         <f t="shared" ref="K6:M6" si="1">SUM(K3:K5)</f>
-        <v>0</v>
+        <v>188.684</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>395.37099999999998</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>583.94100000000003</v>
       </c>
       <c r="N6" s="11">
-        <f t="shared" ref="N6:Q6" si="2">SUM(N3:N5)</f>
-        <v>0</v>
+        <f t="shared" ref="N6:P6" si="2">SUM(N3:N5)</f>
+        <v>747.00400000000002</v>
       </c>
       <c r="O6" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>981.63199999999995</v>
       </c>
       <c r="P6" s="11">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1212.788</v>
+      </c>
+      <c r="Q6" s="145">
+        <f t="shared" ref="Q6:V6" si="3">SUM(Q3:Q5)</f>
+        <v>1364.6759999999999</v>
       </c>
       <c r="R6" s="11">
-        <f t="shared" ref="R6:T6" si="3">SUM(R3:R5)</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="11">
+        <f t="shared" si="3"/>
+        <v>1571.904</v>
+      </c>
+      <c r="S6" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -16436,2464 +16526,2697 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U6" s="14">
-        <f t="shared" ref="U6:X6" si="4">SUM(U3:U5)</f>
+      <c r="U6" s="11">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V6" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="41">
+        <v>12520</v>
+      </c>
+      <c r="G7" s="119">
+        <v>23750</v>
+      </c>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="146"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="114">
+        <v>1970</v>
+      </c>
+      <c r="T7" s="39">
+        <v>2710</v>
+      </c>
+      <c r="U7" s="10">
+        <v>3490</v>
+      </c>
+      <c r="V7" s="152">
+        <v>4330</v>
+      </c>
+      <c r="W7" s="152">
+        <v>4920</v>
+      </c>
+      <c r="X7" s="152">
+        <v>5580</v>
+      </c>
+      <c r="Y7" s="152">
+        <v>6410</v>
+      </c>
+      <c r="Z7" s="152">
+        <v>7240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="10">
+        <v>69</v>
+      </c>
+      <c r="D8" s="10">
+        <v>493</v>
+      </c>
+      <c r="E8" s="114">
+        <v>1453</v>
+      </c>
+      <c r="F8" s="142"/>
+      <c r="G8" s="143"/>
+      <c r="K8" s="39">
+        <v>59.22</v>
+      </c>
+      <c r="L8" s="39">
+        <v>108.83799999999999</v>
+      </c>
+      <c r="M8" s="39">
+        <v>143.13399999999999</v>
+      </c>
+      <c r="N8">
+        <f>D8-M8-L8-K8</f>
+        <v>181.80799999999999</v>
+      </c>
+      <c r="O8" s="39">
+        <v>262.39400000000001</v>
+      </c>
+      <c r="P8" s="39">
+        <v>312.66699999999997</v>
+      </c>
+      <c r="Q8" s="146">
+        <v>368.82400000000001</v>
+      </c>
+      <c r="R8">
+        <f>E8-Q8-P8-O8</f>
+        <v>509.11500000000001</v>
+      </c>
+      <c r="S8" s="114"/>
+      <c r="T8" s="39"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="143"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="146"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="39"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="143"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="146"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="114"/>
+      <c r="T10" s="39"/>
+    </row>
+    <row r="11" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="11">
+        <f t="shared" ref="C11:G11" si="4">SUM(C8:C10)</f>
+        <v>69</v>
+      </c>
+      <c r="D11" s="11">
+        <f t="shared" si="4"/>
+        <v>493</v>
+      </c>
+      <c r="E11" s="14">
+        <f t="shared" si="4"/>
+        <v>1453</v>
+      </c>
+      <c r="F11" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W6" s="11">
+      <c r="G11" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="X6" s="11">
-        <f t="shared" si="4"/>
+      <c r="K11" s="11">
+        <f t="shared" ref="K11:M11" si="5">SUM(K8:K10)</f>
+        <v>59.22</v>
+      </c>
+      <c r="L11" s="11">
+        <f t="shared" si="5"/>
+        <v>108.83799999999999</v>
+      </c>
+      <c r="M11" s="11">
+        <f t="shared" si="5"/>
+        <v>143.13399999999999</v>
+      </c>
+      <c r="N11" s="11">
+        <f t="shared" ref="N11:P11" si="6">SUM(N8:N10)</f>
+        <v>181.80799999999999</v>
+      </c>
+      <c r="O11" s="11">
+        <f t="shared" si="6"/>
+        <v>262.39400000000001</v>
+      </c>
+      <c r="P11" s="11">
+        <f t="shared" si="6"/>
+        <v>312.66699999999997</v>
+      </c>
+      <c r="Q11" s="145">
+        <f t="shared" ref="Q11:V11" si="7">SUM(Q8:Q10)</f>
+        <v>368.82400000000001</v>
+      </c>
+      <c r="R11" s="11">
+        <f t="shared" si="7"/>
+        <v>509.11500000000001</v>
+      </c>
+      <c r="S11" s="14">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="123"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="T11" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="10">
+        <v>131</v>
+      </c>
+      <c r="D12" s="10">
+        <v>961</v>
+      </c>
+      <c r="E12" s="114">
+        <v>2929</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="K12" s="10">
+        <v>92.881</v>
+      </c>
+      <c r="L12" s="10">
+        <v>182.886</v>
+      </c>
+      <c r="M12" s="10">
+        <v>285.50900000000001</v>
+      </c>
+      <c r="N12">
+        <f>D12-M12-L12-K12</f>
+        <v>399.72400000000005</v>
+      </c>
+      <c r="O12" s="10">
+        <v>561.40200000000004</v>
+      </c>
+      <c r="P12" s="10">
+        <v>669.91300000000001</v>
+      </c>
+      <c r="Q12" s="147">
+        <v>747.47900000000004</v>
+      </c>
+      <c r="R12">
+        <f>E12-Q12-P12-O12</f>
+        <v>950.20599999999968</v>
+      </c>
+      <c r="S12" s="15"/>
+      <c r="T12" s="10"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="10">
+        <v>13</v>
+      </c>
+      <c r="D13" s="10">
+        <v>18</v>
+      </c>
+      <c r="E13" s="114">
         <v>144</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="123"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="118"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="123"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="118"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="123"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-    </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="11">
-        <f t="shared" ref="C11:G11" si="5">SUM(C8:C10)</f>
+      <c r="F13" s="39"/>
+      <c r="K13" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="L13" s="10">
+        <v>4.1719999999999997</v>
+      </c>
+      <c r="M13" s="10">
+        <v>4.5540000000000003</v>
+      </c>
+      <c r="N13">
+        <f>D13-M13-L13-K13</f>
+        <v>5.2240000000000011</v>
+      </c>
+      <c r="O13" s="10">
+        <v>10.548999999999999</v>
+      </c>
+      <c r="P13" s="10">
+        <v>36.798999999999999</v>
+      </c>
+      <c r="Q13" s="147">
+        <v>44.645000000000003</v>
+      </c>
+      <c r="R13">
+        <f>E13-Q13-P13-O13</f>
+        <v>52.006999999999991</v>
+      </c>
+      <c r="S13" s="15"/>
+      <c r="T13" s="10"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="10">
+        <v>30</v>
+      </c>
+      <c r="D14" s="10">
+        <v>119</v>
+      </c>
+      <c r="E14" s="15">
+        <v>651</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="K14" s="10">
+        <v>15.686</v>
+      </c>
+      <c r="L14" s="10">
+        <v>21.754000000000001</v>
+      </c>
+      <c r="M14" s="10">
+        <v>33.628</v>
+      </c>
+      <c r="N14">
+        <f>D14-M14-L14-K14</f>
+        <v>47.931999999999995</v>
+      </c>
+      <c r="O14" s="10">
+        <v>174.75700000000001</v>
+      </c>
+      <c r="P14" s="10">
+        <v>174.2</v>
+      </c>
+      <c r="Q14" s="147">
+        <v>151.87799999999999</v>
+      </c>
+      <c r="R14">
+        <f>E14-Q14-P14-O14</f>
+        <v>150.16500000000002</v>
+      </c>
+      <c r="S14" s="15"/>
+      <c r="T14" s="10"/>
+    </row>
+    <row r="15" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11">
+        <f>C6-SUM(C11:C14)</f>
+        <v>-14</v>
+      </c>
+      <c r="D15" s="11">
+        <f>D6-SUM(D11:D14)</f>
+        <v>324</v>
+      </c>
+      <c r="E15" s="14">
+        <f>E6-SUM(E11:E14)</f>
+        <v>-46</v>
+      </c>
+      <c r="F15" s="11">
+        <f>F6-SUM(F11:F14)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="11">
-        <f t="shared" si="5"/>
+      <c r="G15" s="11">
+        <f>G6-SUM(G11:G14)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="14">
-        <f t="shared" si="5"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11">
+        <f>K6-SUM(K11:K14)</f>
+        <v>16.84699999999998</v>
+      </c>
+      <c r="L15" s="11">
+        <f>L6-SUM(L11:L14)</f>
+        <v>77.720999999999947</v>
+      </c>
+      <c r="M15" s="11">
+        <f>M6-SUM(M11:M14)</f>
+        <v>117.11600000000004</v>
+      </c>
+      <c r="N15" s="11">
+        <f>N6-SUM(N11:N14)</f>
+        <v>112.31599999999992</v>
+      </c>
+      <c r="O15" s="11">
+        <f>O6-SUM(O11:O14)</f>
+        <v>-27.470000000000141</v>
+      </c>
+      <c r="P15" s="11">
+        <f>P6-SUM(P11:P14)</f>
+        <v>19.20900000000006</v>
+      </c>
+      <c r="Q15" s="145">
+        <f>Q6-SUM(Q11:Q14)</f>
+        <v>51.849999999999909</v>
+      </c>
+      <c r="R15" s="11">
+        <f>R6-SUM(R11:R14)</f>
+        <v>-89.588999999999714</v>
+      </c>
+      <c r="S15" s="14">
+        <f>S6-SUM(S11:S14)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="11">
-        <f t="shared" si="5"/>
+      <c r="T15" s="11">
+        <f>T6-SUM(T11:T14)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="11">
-        <f t="shared" si="5"/>
+      <c r="U15" s="11">
+        <f>U6-SUM(U11:U14)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="11">
-        <f t="shared" ref="K11" si="6">SUM(K8:K10)</f>
+      <c r="V15" s="11">
+        <f>V6-SUM(V11:V14)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="11">
-        <f t="shared" ref="L11" si="7">SUM(L8:L10)</f>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="10">
+        <v>-534</v>
+      </c>
+      <c r="D16" s="10">
+        <v>-756</v>
+      </c>
+      <c r="E16" s="15">
+        <v>27</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="K16" s="10">
+        <v>-97.5</v>
+      </c>
+      <c r="L16" s="10">
+        <v>-310.23099999999999</v>
+      </c>
+      <c r="M16" s="10">
+        <v>-341.13299999999998</v>
+      </c>
+      <c r="N16">
+        <f>D16-M16-L16-K16</f>
+        <v>-7.1360000000000241</v>
+      </c>
+      <c r="O16" s="10">
+        <v>26.837</v>
+      </c>
+      <c r="P16" s="10">
         <v>0</v>
       </c>
-      <c r="M11" s="11">
-        <f t="shared" ref="M11:Q11" si="8">SUM(M8:M10)</f>
+      <c r="Q16" s="147">
         <v>0</v>
       </c>
-      <c r="N11" s="11">
+      <c r="R16">
+        <f>E16-Q16-P16-O16</f>
+        <v>0.16300000000000026</v>
+      </c>
+      <c r="S16" s="15"/>
+      <c r="T16" s="10"/>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="10">
+        <v>-28</v>
+      </c>
+      <c r="D17" s="10">
+        <v>-361</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-1229</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="K17" s="10">
+        <v>-40.655999999999999</v>
+      </c>
+      <c r="L17" s="10">
+        <v>-66.766000000000005</v>
+      </c>
+      <c r="M17" s="10">
+        <v>-104.375</v>
+      </c>
+      <c r="N17">
+        <f>D17-M17-L17-K17</f>
+        <v>-149.20299999999997</v>
+      </c>
+      <c r="O17" s="10">
+        <v>-263.83499999999998</v>
+      </c>
+      <c r="P17" s="10">
+        <v>-266.96600000000001</v>
+      </c>
+      <c r="Q17" s="147">
+        <v>-310.55500000000001</v>
+      </c>
+      <c r="R17">
+        <f>E17-Q17-P17-O17</f>
+        <v>-387.64399999999995</v>
+      </c>
+      <c r="S17" s="15"/>
+      <c r="T17" s="10"/>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="10">
+        <v>18</v>
+      </c>
+      <c r="D18" s="10">
+        <v>49</v>
+      </c>
+      <c r="E18" s="15">
+        <v>33</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="K18" s="10">
+        <v>7.46</v>
+      </c>
+      <c r="L18" s="10">
+        <v>16.405999999999999</v>
+      </c>
+      <c r="M18" s="10">
+        <v>10.244</v>
+      </c>
+      <c r="N18">
+        <f>D18-M18-L18-K18</f>
+        <v>14.89</v>
+      </c>
+      <c r="O18" s="10">
+        <v>-4.1369999999999996</v>
+      </c>
+      <c r="P18" s="10">
+        <v>5.0229999999999997</v>
+      </c>
+      <c r="Q18" s="147">
+        <v>21.901</v>
+      </c>
+      <c r="R18">
+        <f>E18-Q18-P18-O18</f>
+        <v>10.213000000000001</v>
+      </c>
+      <c r="S18" s="15"/>
+      <c r="T18" s="10"/>
+    </row>
+    <row r="19" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="11">
+        <f t="shared" ref="C19:D19" si="8">C15+SUM(C16:C18)</f>
+        <v>-558</v>
+      </c>
+      <c r="D19" s="11">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="11">
-        <f t="shared" ref="R11:T11" si="9">SUM(R8:R10)</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="11">
+        <v>-744</v>
+      </c>
+      <c r="E19" s="14">
+        <f t="shared" ref="E19:G19" si="9">E15+SUM(E16:E18)</f>
+        <v>-1215</v>
+      </c>
+      <c r="F19" s="11">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T11" s="11">
+      <c r="G19" s="11">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U11" s="14">
-        <f t="shared" ref="U11:X11" si="10">SUM(U8:U10)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="11">
+      <c r="K19" s="11">
+        <f t="shared" ref="K19:M19" si="10">K15+SUM(K16:K18)</f>
+        <v>-113.84900000000002</v>
+      </c>
+      <c r="L19" s="11">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="11">
+        <v>-282.87000000000006</v>
+      </c>
+      <c r="M19" s="11">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="11">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="40"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="40"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="40"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-    </row>
-    <row r="16" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="11">
-        <f t="shared" ref="C16:D16" si="11">C6-SUM(C11:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="11">
+        <v>-318.14799999999997</v>
+      </c>
+      <c r="N19" s="11">
+        <f t="shared" ref="N19:P19" si="11">N15+SUM(N16:N18)</f>
+        <v>-29.133000000000095</v>
+      </c>
+      <c r="O19" s="11">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="14">
-        <f t="shared" ref="E16:G16" si="12">E6-SUM(E11:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="11">
+        <v>-268.60500000000013</v>
+      </c>
+      <c r="P19" s="11">
+        <f t="shared" si="11"/>
+        <v>-242.73399999999992</v>
+      </c>
+      <c r="Q19" s="145">
+        <f t="shared" ref="Q19:V19" si="12">Q15+SUM(Q16:Q18)</f>
+        <v>-236.80400000000009</v>
+      </c>
+      <c r="R19" s="11">
+        <f t="shared" si="12"/>
+        <v>-466.85699999999963</v>
+      </c>
+      <c r="S19" s="14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="G16" s="11">
+      <c r="T19" s="11">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11">
-        <f t="shared" ref="K16" si="13">K6-SUM(K11:K15)</f>
+      <c r="U19" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L16" s="11">
-        <f t="shared" ref="L16" si="14">L6-SUM(L11:L15)</f>
+      <c r="V19" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M16" s="11">
-        <f t="shared" ref="M16:Q16" si="15">M6-SUM(M11:M15)</f>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="10">
+        <v>36</v>
+      </c>
+      <c r="D20" s="10">
+        <v>119</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-48</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="K20" s="10">
+        <v>15.398999999999999</v>
+      </c>
+      <c r="L20" s="10">
+        <v>40.151000000000003</v>
+      </c>
+      <c r="M20" s="10">
+        <v>41.658999999999999</v>
+      </c>
+      <c r="N20">
+        <f>D20-M20-L20-K20</f>
+        <v>21.791000000000004</v>
+      </c>
+      <c r="O20" s="10">
+        <v>46.036000000000001</v>
+      </c>
+      <c r="P20" s="10">
+        <v>47.774999999999999</v>
+      </c>
+      <c r="Q20" s="147">
+        <v>-126.68</v>
+      </c>
+      <c r="R20">
+        <f>E20-Q20-P20-O20</f>
+        <v>-15.130999999999993</v>
+      </c>
+      <c r="S20" s="15"/>
+      <c r="T20" s="10"/>
+    </row>
+    <row r="21" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="11">
+        <f>C19-SUM(C20:C20)</f>
+        <v>-594</v>
+      </c>
+      <c r="D21" s="11">
+        <f>D19-SUM(D20:D20)</f>
+        <v>-863</v>
+      </c>
+      <c r="E21" s="14">
+        <f>E19-SUM(E20:E20)</f>
+        <v>-1167</v>
+      </c>
+      <c r="F21" s="11">
+        <f>F19-SUM(F20:F20)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="11">
-        <f t="shared" si="15"/>
+      <c r="G21" s="11">
+        <f>G19-SUM(G20:G20)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="11">
-        <f t="shared" si="15"/>
+      <c r="K21" s="11">
+        <f>K19-SUM(K20:K20)</f>
+        <v>-129.24800000000002</v>
+      </c>
+      <c r="L21" s="11">
+        <f>L19-SUM(L20:L20)</f>
+        <v>-323.02100000000007</v>
+      </c>
+      <c r="M21" s="11">
+        <f>M19-SUM(M20:M20)</f>
+        <v>-359.80699999999996</v>
+      </c>
+      <c r="N21" s="11">
+        <f>N19-SUM(N20:N20)</f>
+        <v>-50.924000000000099</v>
+      </c>
+      <c r="O21" s="11">
+        <f>O19-SUM(O20:O20)</f>
+        <v>-314.64100000000013</v>
+      </c>
+      <c r="P21" s="11">
+        <f>P19-SUM(P20:P20)</f>
+        <v>-290.5089999999999</v>
+      </c>
+      <c r="Q21" s="145">
+        <f>Q19-SUM(Q20:Q20)</f>
+        <v>-110.12400000000008</v>
+      </c>
+      <c r="R21" s="11">
+        <f>R19-SUM(R20:R20)</f>
+        <v>-451.72599999999966</v>
+      </c>
+      <c r="S21" s="14">
+        <f>S19-SUM(S20:S20)</f>
         <v>0</v>
       </c>
-      <c r="P16" s="11">
-        <f t="shared" si="15"/>
+      <c r="T21" s="11">
+        <f>T19-SUM(T20:T20)</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="11">
-        <f t="shared" si="15"/>
+      <c r="U21" s="11">
+        <f>U19-SUM(U20:U20)</f>
         <v>0</v>
       </c>
-      <c r="R16" s="11">
-        <f t="shared" ref="R16:T16" si="16">R6-SUM(R11:R15)</f>
+      <c r="V21" s="11">
+        <f>V19-SUM(V20:V20)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="11">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="11">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="14">
-        <f t="shared" ref="U16:X16" si="17">U6-SUM(U11:U15)</f>
-        <v>0</v>
-      </c>
-      <c r="V16" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-    </row>
-    <row r="20" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="11">
-        <f t="shared" ref="C20:D20" si="18">C16+SUM(C17:C19)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="11">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="14">
-        <f t="shared" ref="E20:G20" si="19">E16+SUM(E17:E19)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="11">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="11">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="11">
-        <f t="shared" ref="K20" si="20">K16+SUM(K17:K19)</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="11">
-        <f t="shared" ref="L20" si="21">L16+SUM(L17:L19)</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" ref="M20:Q20" si="22">M16+SUM(M17:M19)</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="11">
-        <f t="shared" ref="R20:T20" si="23">R16+SUM(R17:R19)</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="14">
-        <f t="shared" ref="U20:X20" si="24">U16+SUM(U17:U19)</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="11">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="11">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="11">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="15"/>
+        <v>194</v>
+      </c>
+      <c r="C22" s="10">
+        <v>192</v>
+      </c>
+      <c r="D22" s="10">
+        <v>218</v>
+      </c>
+      <c r="E22" s="15">
+        <v>436</v>
+      </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
+      <c r="K22" s="10">
+        <v>209.22800000000001</v>
+      </c>
+      <c r="L22" s="10">
+        <v>209.626</v>
+      </c>
+      <c r="M22" s="10">
+        <v>213.80600000000001</v>
+      </c>
+      <c r="N22" s="10">
+        <v>213.80600000000001</v>
+      </c>
+      <c r="O22" s="10">
+        <v>249.29300000000001</v>
+      </c>
+      <c r="P22" s="10">
+        <v>486.59100000000001</v>
+      </c>
+      <c r="Q22" s="147">
+        <v>497.88600000000002</v>
+      </c>
+      <c r="R22" s="147">
+        <v>497.88600000000002</v>
+      </c>
+      <c r="S22" s="15"/>
       <c r="T22" s="10"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-    </row>
-    <row r="23" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="11">
-        <f t="shared" ref="C23:D23" si="25">C20-SUM(C21:C22)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="11">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="14">
-        <f t="shared" ref="E23:G23" si="26">E20-SUM(E21:E22)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="11">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="11">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="11">
-        <f t="shared" ref="K23" si="27">K20-SUM(K21:K22)</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="11">
-        <f t="shared" ref="L23" si="28">L20-SUM(L21:L22)</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="11">
-        <f t="shared" ref="M23:Q23" si="29">M20-SUM(M21:M22)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="11">
-        <f t="shared" ref="R23:T23" si="30">R20-SUM(R21:R22)</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="11">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="11">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="14">
-        <f t="shared" ref="U23:X23" si="31">U20-SUM(U21:U22)</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="11">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="11">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="11">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-    </row>
-    <row r="25" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="2" t="e">
-        <f>C23/C24</f>
+        <v>11</v>
+      </c>
+      <c r="C23" s="2">
+        <f>C21/C22</f>
+        <v>-3.09375</v>
+      </c>
+      <c r="D23" s="117">
+        <f>D21/D22</f>
+        <v>-3.9587155963302751</v>
+      </c>
+      <c r="E23" s="34">
+        <f t="shared" ref="E23:G23" si="13">E21/E22</f>
+        <v>-2.676605504587156</v>
+      </c>
+      <c r="F23" s="2" t="e">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D25" s="121" t="e">
-        <f>D23/D24</f>
+      <c r="G23" s="2" t="e">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="35" t="e">
-        <f t="shared" ref="E25:G25" si="32">E23/E24</f>
+      <c r="K23" s="2">
+        <f t="shared" ref="K23:M23" si="14">K21/K22</f>
+        <v>-0.61773758770336673</v>
+      </c>
+      <c r="L23" s="2">
+        <f t="shared" si="14"/>
+        <v>-1.5409395781057695</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="14"/>
+        <v>-1.6828667109435653</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" ref="N23:P23" si="15">N21/N22</f>
+        <v>-0.23817853568188027</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="15"/>
+        <v>-1.2621333130091905</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="15"/>
+        <v>-0.59702912713140999</v>
+      </c>
+      <c r="Q23" s="148">
+        <f t="shared" ref="Q23:V23" si="16">Q21/Q22</f>
+        <v>-0.22118316241067248</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="16"/>
+        <v>-0.90728801372201595</v>
+      </c>
+      <c r="S23" s="34" t="e">
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F25" s="2" t="e">
-        <f t="shared" si="32"/>
+      <c r="T23" s="2" t="e">
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G25" s="2" t="e">
-        <f t="shared" si="32"/>
+      <c r="U23" s="2" t="e">
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K25" s="2" t="e">
-        <f t="shared" ref="K25:M25" si="33">K23/K24</f>
+      <c r="V23" s="2" t="e">
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L25" s="2" t="e">
-        <f t="shared" si="33"/>
+    </row>
+    <row r="24" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="42">
+        <v>-2.71</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-0.45</v>
+      </c>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="149"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="115">
+        <v>-0.9</v>
+      </c>
+      <c r="T24" s="43">
+        <v>-0.79</v>
+      </c>
+      <c r="U24" s="1">
+        <v>-0.64</v>
+      </c>
+      <c r="V24" s="1">
+        <v>-0.46</v>
+      </c>
+      <c r="W24" s="1">
+        <v>-0.54</v>
+      </c>
+      <c r="X24" s="1">
+        <v>-0.38</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>-0.17</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="3">
+        <f>1-C11/C6</f>
+        <v>0.6986899563318778</v>
+      </c>
+      <c r="D25" s="38">
+        <f>1-D11/D6</f>
+        <v>0.74255874673629241</v>
+      </c>
+      <c r="E25" s="6">
+        <f>1-E11/E6</f>
+        <v>0.71681933346326254</v>
+      </c>
+      <c r="F25" s="38" t="e">
+        <f>1-F11/F6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M25" s="2" t="e">
-        <f t="shared" si="33"/>
+      <c r="G25" s="38" t="e">
+        <f>1-G11/G6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N25" s="2" t="e">
-        <f t="shared" ref="N25:Q25" si="34">N23/N24</f>
+      <c r="K25" s="3">
+        <f>1-K11/K6</f>
+        <v>0.68614190922388762</v>
+      </c>
+      <c r="L25" s="38">
+        <f>1-L11/L6</f>
+        <v>0.7247193142643239</v>
+      </c>
+      <c r="M25" s="3">
+        <f>1-M11/M6</f>
+        <v>0.75488277069087462</v>
+      </c>
+      <c r="N25" s="38">
+        <f>1-N11/N6</f>
+        <v>0.75661709977456615</v>
+      </c>
+      <c r="O25" s="3">
+        <f>1-O11/O6</f>
+        <v>0.73269616312426655</v>
+      </c>
+      <c r="P25" s="3">
+        <f>1-P11/P6</f>
+        <v>0.74219154543085852</v>
+      </c>
+      <c r="Q25" s="38">
+        <f>1-Q11/Q6</f>
+        <v>0.72973511661376034</v>
+      </c>
+      <c r="R25" s="3">
+        <f>1-R11/R6</f>
+        <v>0.67611571699035056</v>
+      </c>
+      <c r="S25" s="6" t="e">
+        <f>1-S11/S6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O25" s="2" t="e">
-        <f t="shared" si="34"/>
+      <c r="T25" s="3" t="e">
+        <f>1-T11/T6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P25" s="2" t="e">
-        <f t="shared" si="34"/>
+      <c r="U25" s="3" t="e">
+        <f>1-U11/U6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q25" s="2" t="e">
-        <f t="shared" si="34"/>
+      <c r="V25" s="3" t="e">
+        <f>1-V11/V6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R25" s="2" t="e">
-        <f t="shared" ref="R25:T25" si="35">R23/R24</f>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="4">
+        <f>C21/C6</f>
+        <v>-2.5938864628820961</v>
+      </c>
+      <c r="D26" s="4">
+        <f>D21/D6</f>
+        <v>-0.4506527415143603</v>
+      </c>
+      <c r="E26" s="7">
+        <f>E21/E6</f>
+        <v>-0.22744104463067627</v>
+      </c>
+      <c r="F26" s="4" t="e">
+        <f>F21/F6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="2" t="e">
-        <f t="shared" si="35"/>
+      <c r="G26" s="4" t="e">
+        <f>G21/G6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T25" s="2" t="e">
-        <f t="shared" si="35"/>
+      <c r="K26" s="4">
+        <f>K21/K6</f>
+        <v>-0.6849971380721207</v>
+      </c>
+      <c r="L26" s="4">
+        <f>L21/L6</f>
+        <v>-0.81700731717804309</v>
+      </c>
+      <c r="M26" s="4">
+        <f>M21/M6</f>
+        <v>-0.6161701267765064</v>
+      </c>
+      <c r="N26" s="4">
+        <f>N21/N6</f>
+        <v>-6.8170987036214131E-2</v>
+      </c>
+      <c r="O26" s="4">
+        <f>O21/O6</f>
+        <v>-0.32052846687964548</v>
+      </c>
+      <c r="P26" s="4">
+        <f>P21/P6</f>
+        <v>-0.23953815506090093</v>
+      </c>
+      <c r="Q26" s="141">
+        <f>Q21/Q6</f>
+        <v>-8.0696077310658421E-2</v>
+      </c>
+      <c r="R26" s="4">
+        <f>R21/R6</f>
+        <v>-0.28737505598306234</v>
+      </c>
+      <c r="S26" s="7" t="e">
+        <f>S21/S6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U25" s="35" t="e">
-        <f t="shared" ref="U25:X25" si="36">U23/U24</f>
+      <c r="T26" s="4" t="e">
+        <f>T21/T6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V25" s="2" t="e">
-        <f t="shared" si="36"/>
+      <c r="U26" s="4" t="e">
+        <f>U21/U6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W25" s="2" t="e">
-        <f t="shared" si="36"/>
+      <c r="V26" s="4" t="e">
+        <f>V21/V6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X25" s="2" t="e">
-        <f t="shared" si="36"/>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38">
+        <f>D6/C6-1</f>
+        <v>7.3624454148471621</v>
+      </c>
+      <c r="E27" s="6">
+        <f>E6/D6-1</f>
+        <v>1.679373368146214</v>
+      </c>
+      <c r="F27" s="38">
+        <f>F6/E6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="G27" s="38" t="e">
+        <f>G6/F6-1</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="26" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="43"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="119"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="44"/>
-      <c r="X26" s="44"/>
-    </row>
-    <row r="27" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="e">
-        <f>1-C11/C6</f>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4">
+        <f>O6/K6-1</f>
+        <v>4.2025184965338873</v>
+      </c>
+      <c r="P27" s="4">
+        <f>P6/L6-1</f>
+        <v>2.0674682766313159</v>
+      </c>
+      <c r="Q27" s="141">
+        <f>Q6/M6-1</f>
+        <v>1.3370100746479521</v>
+      </c>
+      <c r="R27" s="4">
+        <f>R6/N6-1</f>
+        <v>1.1042778887395515</v>
+      </c>
+      <c r="S27" s="7">
+        <f>S6/O6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="T27" s="4">
+        <f>T6/P6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="U27" s="4">
+        <f>U6/Q6-1</f>
+        <v>-1</v>
+      </c>
+      <c r="V27" s="4">
+        <f>V6/R6-1</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="4">
+        <f>C12/C6</f>
+        <v>0.57205240174672489</v>
+      </c>
+      <c r="D28" s="4">
+        <f>D12/D6</f>
+        <v>0.50182767624020885</v>
+      </c>
+      <c r="E28" s="7">
+        <f>E12/E6</f>
+        <v>0.57084389007990644</v>
+      </c>
+      <c r="F28" s="4" t="e">
+        <f>F12/F6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D27" s="39" t="e">
-        <f>1-D11/D6</f>
+      <c r="G28" s="4" t="e">
+        <f>G12/G6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="6" t="e">
-        <f t="shared" ref="E27:G27" si="37">1-E11/E6</f>
+      <c r="K28" s="4">
+        <f>K12/K6</f>
+        <v>0.49225689512624282</v>
+      </c>
+      <c r="L28" s="4">
+        <f>L12/L6</f>
+        <v>0.46256806897825081</v>
+      </c>
+      <c r="M28" s="4">
+        <f>M12/M6</f>
+        <v>0.48893466976971989</v>
+      </c>
+      <c r="N28" s="4">
+        <f>N12/N6</f>
+        <v>0.53510289101530917</v>
+      </c>
+      <c r="O28" s="4">
+        <f>O12/O6</f>
+        <v>0.57190678380492899</v>
+      </c>
+      <c r="P28" s="4">
+        <f>P12/P6</f>
+        <v>0.55237436386243932</v>
+      </c>
+      <c r="Q28" s="141">
+        <f>Q12/Q6</f>
+        <v>0.54773367451321786</v>
+      </c>
+      <c r="R28" s="4">
+        <f>R12/R6</f>
+        <v>0.60449365864582039</v>
+      </c>
+      <c r="S28" s="7" t="e">
+        <f>S12/S6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F27" s="39" t="e">
-        <f t="shared" si="37"/>
+      <c r="T28" s="4" t="e">
+        <f>T12/T6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G27" s="39" t="e">
-        <f t="shared" si="37"/>
+      <c r="U28" s="4" t="e">
+        <f>U12/U6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="3" t="e">
-        <f t="shared" ref="K27:M27" si="38">1-K11/K6</f>
+      <c r="V28" s="4" t="e">
+        <f>V12/V6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L27" s="3" t="e">
-        <f t="shared" si="38"/>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="4">
+        <f>C13/C6</f>
+        <v>5.6768558951965066E-2</v>
+      </c>
+      <c r="D29" s="4">
+        <f>D13/D6</f>
+        <v>9.3994778067885126E-3</v>
+      </c>
+      <c r="E29" s="7">
+        <f>E13/E6</f>
+        <v>2.8064704735918926E-2</v>
+      </c>
+      <c r="F29" s="4" t="e">
+        <f>F13/F6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M27" s="3" t="e">
-        <f t="shared" si="38"/>
+      <c r="G29" s="4" t="e">
+        <f>G13/G6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N27" s="3" t="e">
-        <f t="shared" ref="N27:Q27" si="39">1-N11/N6</f>
+      <c r="K29" s="4">
+        <f>K13/K6</f>
+        <v>2.146445909563079E-2</v>
+      </c>
+      <c r="L29" s="4">
+        <f>L13/L6</f>
+        <v>1.0552114343237112E-2</v>
+      </c>
+      <c r="M29" s="4">
+        <f>M13/M6</f>
+        <v>7.7987330911855821E-3</v>
+      </c>
+      <c r="N29" s="4">
+        <f>N13/N6</f>
+        <v>6.9932691123474585E-3</v>
+      </c>
+      <c r="O29" s="4">
+        <f>O13/O6</f>
+        <v>1.0746389685747816E-2</v>
+      </c>
+      <c r="P29" s="4">
+        <f>P13/P6</f>
+        <v>3.0342483599771763E-2</v>
+      </c>
+      <c r="Q29" s="141">
+        <f>Q13/Q6</f>
+        <v>3.2714724960356892E-2</v>
+      </c>
+      <c r="R29" s="4">
+        <f>R13/R6</f>
+        <v>3.3085353812955492E-2</v>
+      </c>
+      <c r="S29" s="7" t="e">
+        <f>S13/S6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="3" t="e">
-        <f t="shared" si="39"/>
+      <c r="T29" s="4" t="e">
+        <f>T13/T6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P27" s="39" t="e">
-        <f t="shared" si="39"/>
+      <c r="U29" s="4" t="e">
+        <f>U13/U6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="3" t="e">
-        <f t="shared" si="39"/>
+      <c r="V29" s="4" t="e">
+        <f>V13/V6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R27" s="39" t="e">
-        <f t="shared" ref="R27:T27" si="40">1-R11/R6</f>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="141">
+        <f t="shared" ref="C30:D30" si="17">C14/C6</f>
+        <v>0.13100436681222707</v>
+      </c>
+      <c r="D30" s="141">
+        <f t="shared" si="17"/>
+        <v>6.2140992167101824E-2</v>
+      </c>
+      <c r="E30" s="7">
+        <f>E14/E6</f>
+        <v>0.12687585266030013</v>
+      </c>
+      <c r="F30" s="141" t="e">
+        <f t="shared" ref="F30:G30" si="18">F14/F6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="3" t="e">
-        <f t="shared" si="40"/>
+      <c r="G30" s="141" t="e">
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T27" s="3" t="e">
-        <f t="shared" si="40"/>
+      <c r="K30" s="141">
+        <f t="shared" ref="K30:T30" si="19">K14/K6</f>
+        <v>8.3133705030633234E-2</v>
+      </c>
+      <c r="L30" s="141">
+        <f t="shared" si="19"/>
+        <v>5.502173907545066E-2</v>
+      </c>
+      <c r="M30" s="141">
+        <f t="shared" si="19"/>
+        <v>5.7588009747560114E-2</v>
+      </c>
+      <c r="N30" s="141">
+        <f t="shared" si="19"/>
+        <v>6.4165653731439176E-2</v>
+      </c>
+      <c r="O30" s="141">
+        <f t="shared" si="19"/>
+        <v>0.17802699993480248</v>
+      </c>
+      <c r="P30" s="141">
+        <f t="shared" si="19"/>
+        <v>0.1436359858441871</v>
+      </c>
+      <c r="Q30" s="141">
+        <f t="shared" si="19"/>
+        <v>0.11129235071181731</v>
+      </c>
+      <c r="R30" s="141">
+        <f t="shared" si="19"/>
+        <v>9.5530643092707965E-2</v>
+      </c>
+      <c r="S30" s="7" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U27" s="6" t="e">
-        <f t="shared" ref="U27:X27" si="41">1-U11/U6</f>
+      <c r="T30" s="141" t="e">
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V27" s="3" t="e">
-        <f t="shared" si="41"/>
+      <c r="U30" s="141" t="e">
+        <f t="shared" ref="U30:V30" si="20">U14/U6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W27" s="3" t="e">
-        <f t="shared" si="41"/>
+      <c r="V30" s="141" t="e">
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X27" s="3" t="e">
-        <f t="shared" si="41"/>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4">
+        <f>D3/C3-1</f>
+        <v>7.3624454148471621</v>
+      </c>
+      <c r="E31" s="7">
+        <f>E3/D3-1</f>
+        <v>1.679373368146214</v>
+      </c>
+      <c r="F31" s="4">
+        <f>F3/E3-1</f>
+        <v>-1</v>
+      </c>
+      <c r="G31" s="4" t="e">
+        <f>G3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="4" t="e">
-        <f>C23/C6</f>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="141"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="e">
+        <f>D4/C4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D28" s="4" t="e">
-        <f>D23/D6</f>
+      <c r="E32" s="7" t="e">
+        <f>E4/D4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="7" t="e">
-        <f t="shared" ref="E28:G28" si="42">E23/E6</f>
+      <c r="F32" s="4" t="e">
+        <f>F4/E4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F28" s="4" t="e">
-        <f t="shared" si="42"/>
+      <c r="G32" s="4" t="e">
+        <f>G4/F4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G28" s="4" t="e">
-        <f t="shared" si="42"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="141"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="4"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="38" t="e">
+        <f>C23/#REF!-1</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D33" s="38">
+        <f>D23/C23-1</f>
+        <v>0.27958483921786681</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" ref="E33:G33" si="21">E23/D23-1</f>
+        <v>-0.32387022016222478</v>
+      </c>
+      <c r="F33" s="38" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="4" t="e">
-        <f t="shared" ref="K28:M28" si="43">K23/K6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L28" s="4" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M28" s="4" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N28" s="4" t="e">
-        <f t="shared" ref="N28:Q28" si="44">N23/N6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="4" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P28" s="4" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q28" s="4" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R28" s="4" t="e">
-        <f t="shared" ref="R28:T28" si="45">R23/R6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S28" s="4" t="e">
-        <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T28" s="4" t="e">
-        <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U28" s="7" t="e">
-        <f t="shared" ref="U28:X28" si="46">U23/U6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V28" s="4" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W28" s="4" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X28" s="4" t="e">
-        <f t="shared" si="46"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39" t="e">
-        <f>D6/C6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="6" t="e">
-        <f t="shared" ref="E29:G29" si="47">E6/D6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F29" s="39" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G29" s="39" t="e">
-        <f t="shared" si="47"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4" t="e">
-        <f t="shared" ref="O29" si="48">O6/K6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P29" s="4" t="e">
-        <f t="shared" ref="P29" si="49">P6/L6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q29" s="4" t="e">
-        <f t="shared" ref="Q29" si="50">Q6/M6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R29" s="4" t="e">
-        <f t="shared" ref="R29" si="51">R6/N6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S29" s="4" t="e">
-        <f t="shared" ref="S29" si="52">S6/O6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T29" s="4" t="e">
-        <f t="shared" ref="T29" si="53">T6/P6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U29" s="7" t="e">
-        <f t="shared" ref="U29" si="54">U6/Q6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V29" s="4" t="e">
-        <f t="shared" ref="V29" si="55">V6/R6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W29" s="4" t="e">
-        <f t="shared" ref="W29" si="56">W6/S6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X29" s="4" t="e">
-        <f t="shared" ref="X29" si="57">X6/T6-1</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="4" t="e">
-        <f>C12/C6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D30" s="4" t="e">
-        <f>D12/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E30" s="7" t="e">
-        <f t="shared" ref="E30:G30" si="58">E12/E6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F30" s="4" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="4" t="e">
-        <f t="shared" si="58"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="4" t="e">
-        <f t="shared" ref="K30:M30" si="59">K12/K6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" s="4" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="4" t="e">
-        <f t="shared" si="59"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="4" t="e">
-        <f t="shared" ref="N30:Q30" si="60">N12/N6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="4" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P30" s="4" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q30" s="4" t="e">
-        <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R30" s="4" t="e">
-        <f t="shared" ref="R30:T30" si="61">R12/R6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S30" s="4" t="e">
-        <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" s="4" t="e">
-        <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U30" s="7" t="e">
-        <f t="shared" ref="U30:X30" si="62">U12/U6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V30" s="4" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W30" s="4" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X30" s="4" t="e">
-        <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="4" t="e">
-        <f t="shared" ref="C31" si="63">C13/C6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D31" s="4" t="e">
-        <f>D13/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E31" s="7" t="e">
-        <f t="shared" ref="E31:G31" si="64">E13/E6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F31" s="4" t="e">
-        <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="4" t="e">
-        <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="4" t="e">
-        <f t="shared" ref="K31:M31" si="65">K13/K6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L31" s="4" t="e">
-        <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="4" t="e">
-        <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N31" s="4" t="e">
-        <f t="shared" ref="N31:Q31" si="66">N13/N6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="4" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P31" s="4" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q31" s="4" t="e">
-        <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R31" s="4" t="e">
-        <f t="shared" ref="R31:T31" si="67">R13/R6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S31" s="4" t="e">
-        <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" s="4" t="e">
-        <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U31" s="7" t="e">
-        <f t="shared" ref="U31:X31" si="68">U13/U6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V31" s="4" t="e">
-        <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W31" s="4" t="e">
-        <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X31" s="4" t="e">
-        <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="4" t="e">
-        <f>C15/C6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D32" s="4" t="e">
-        <f>D15/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E32" s="7" t="e">
-        <f t="shared" ref="E32:G32" si="69">E15/E6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F32" s="4" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G32" s="4" t="e">
-        <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="4" t="e">
-        <f t="shared" ref="K32:M32" si="70">K15/K6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L32" s="4" t="e">
-        <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="4" t="e">
-        <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N32" s="4" t="e">
-        <f t="shared" ref="N32:Q32" si="71">N15/N6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="4" t="e">
-        <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P32" s="4" t="e">
-        <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q32" s="4" t="e">
-        <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R32" s="4" t="e">
-        <f t="shared" ref="R32:T32" si="72">R15/R6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S32" s="4" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T32" s="4" t="e">
-        <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U32" s="7" t="e">
-        <f t="shared" ref="U32:X32" si="73">U15/U6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V32" s="4" t="e">
-        <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W32" s="4" t="e">
-        <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X32" s="4" t="e">
-        <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4" t="e">
-        <f t="shared" ref="D33:D34" si="74">D3/C3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E33" s="7" t="e">
-        <f t="shared" ref="E33:E34" si="75">E3/D3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F33" s="4" t="e">
-        <f t="shared" ref="F33:F34" si="76">F3/E3-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="4" t="e">
-        <f t="shared" ref="G33:G34" si="77">G3/F3-1</f>
+      <c r="G33" s="38" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4" t="e">
-        <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E34" s="7" t="e">
-        <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F34" s="4" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="4" t="e">
-        <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="39" t="e">
-        <f>C25/#REF!-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D35" s="39" t="e">
-        <f>D25/C25-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E35" s="6" t="e">
-        <f t="shared" ref="E35:G35" si="78">E25/D25-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F35" s="39" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="39" t="e">
-        <f t="shared" si="78"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4" t="e">
-        <f t="shared" ref="O35" si="79">O23/K23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P35" s="4" t="e">
-        <f t="shared" ref="P35" si="80">P23/L23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q35" s="4" t="e">
-        <f t="shared" ref="Q35" si="81">Q23/M23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R35" s="4" t="e">
-        <f t="shared" ref="R35" si="82">R23/N23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S35" s="4" t="e">
-        <f t="shared" ref="S35" si="83">S23/O23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T35" s="4" t="e">
-        <f t="shared" ref="T35" si="84">T23/P23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U35" s="7" t="e">
-        <f t="shared" ref="U35" si="85">U23/Q23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V35" s="4" t="e">
-        <f t="shared" ref="V35" si="86">V23/R23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W35" s="4" t="e">
-        <f t="shared" ref="W35" si="87">W23/S23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X35" s="4" t="e">
-        <f t="shared" ref="X35" si="88">X23/T23-1</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="47" t="e">
-        <f>C17/C6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D36" s="47" t="e">
-        <f>D17/D6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E36" s="48" t="e">
-        <f t="shared" ref="E36:G36" si="89">E17/E6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F36" s="47" t="e">
-        <f t="shared" si="89"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G36" s="47" t="e">
-        <f t="shared" si="89"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="O33" s="4">
+        <f t="shared" ref="O33" si="22">O21/K21-1</f>
+        <v>1.4343974374845265</v>
+      </c>
+      <c r="P33" s="4">
+        <f t="shared" ref="P33" si="23">P21/L21-1</f>
+        <v>-0.10064980295398807</v>
+      </c>
+      <c r="Q33" s="141">
+        <f t="shared" ref="Q33" si="24">Q21/M21-1</f>
+        <v>-0.69393591564366419</v>
+      </c>
+      <c r="R33" s="4">
+        <f t="shared" ref="R33" si="25">R21/N21-1</f>
+        <v>7.8705914696410098</v>
+      </c>
+      <c r="S33" s="7">
+        <f t="shared" ref="S33" si="26">S21/O21-1</f>
+        <v>-1</v>
+      </c>
+      <c r="T33" s="4">
+        <f t="shared" ref="T33" si="27">T21/P21-1</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C37+C38-C65-C51</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="11">
+        <f>D37+D38-D65-D51</f>
+        <v>493</v>
+      </c>
+      <c r="E36" s="14">
+        <f>E37+E38-E65-E51</f>
+        <v>2037</v>
+      </c>
+      <c r="F36" s="11">
+        <f>F37+F38-F65-F51</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="11">
+        <f>G37+G38-G65-G51</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="11">
+        <f>K37+K38-K65-K51</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="11">
+        <f>L37+L38-L65-L51</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="11">
+        <f>M37+M38-M65-M51</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="11">
+        <f>N37+N38-N65-N51</f>
+        <v>0</v>
+      </c>
+      <c r="O36" s="11">
+        <f>O37+O38-O65-O51</f>
+        <v>625.83400000000006</v>
+      </c>
+      <c r="P36" s="11">
+        <f>P37+P38-P65-P51</f>
+        <v>360.14600000000019</v>
+      </c>
+      <c r="Q36" s="145">
+        <f>Q37+Q38-Q65-Q51</f>
+        <v>1065.7889999999998</v>
+      </c>
+      <c r="R36" s="11">
+        <f>R37+R38-R65-R51</f>
+        <v>2037</v>
+      </c>
+      <c r="S36" s="14">
+        <f>S37+S38-S65-S51</f>
+        <v>0</v>
+      </c>
+      <c r="T36" s="11">
+        <f>T37+T38-T65-T51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="49" t="e">
-        <f t="shared" ref="C37:D37" si="90">-C17/C16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D37" s="47" t="e">
-        <f t="shared" si="90"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E37" s="48" t="e">
-        <f t="shared" ref="E37:G37" si="91">-E17/E16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F37" s="47" t="e">
-        <f t="shared" si="91"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G37" s="47" t="e">
-        <f t="shared" si="91"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-    </row>
-    <row r="40" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="11">
-        <f t="shared" ref="C40" si="92">C41+C42-C64-C55</f>
+        <v>13</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10">
+        <v>1361</v>
+      </c>
+      <c r="E37" s="15">
+        <v>3127</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10">
+        <v>1276.4559999999999</v>
+      </c>
+      <c r="P37" s="10">
+        <v>1152.883</v>
+      </c>
+      <c r="Q37" s="147">
+        <v>1894.3989999999999</v>
+      </c>
+      <c r="R37" s="10">
+        <f>E37</f>
+        <v>3127</v>
+      </c>
+      <c r="S37" s="15"/>
+      <c r="T37" s="10"/>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10">
+        <v>37</v>
+      </c>
+      <c r="E38" s="15">
+        <v>819</v>
+      </c>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10">
+        <v>624.25</v>
+      </c>
+      <c r="P38" s="10">
+        <v>560.173</v>
+      </c>
+      <c r="Q38" s="147">
+        <v>596.77700000000004</v>
+      </c>
+      <c r="R38" s="10">
+        <f t="shared" ref="R38:R41" si="28">E38</f>
+        <v>819</v>
+      </c>
+      <c r="S38" s="15"/>
+      <c r="T38" s="10"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10">
         <v>0</v>
       </c>
-      <c r="D40" s="11">
-        <f t="shared" ref="D40:G40" si="93">D41+D42-D64-D55</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="14">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="11">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="11">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="11">
-        <f t="shared" ref="K40:Q40" si="94">K41+K42-K64-K55</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="N40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="O40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="P40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="11">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="R40" s="11">
-        <f t="shared" ref="R40:T40" si="95">R41+R42-R64-R55</f>
-        <v>0</v>
-      </c>
-      <c r="S40" s="11">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="T40" s="11">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="14">
-        <f t="shared" ref="U40:X40" si="96">U41+U42-U64-U55</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="11">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="11">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="X40" s="11">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="E39" s="15">
+        <v>34</v>
+      </c>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="147">
+        <v>47.448999999999998</v>
+      </c>
+      <c r="R39" s="10">
+        <f t="shared" si="28"/>
+        <v>34</v>
+      </c>
+      <c r="S39" s="15"/>
+      <c r="T39" s="10"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10">
+        <v>417</v>
+      </c>
+      <c r="E40" s="15">
+        <v>3169</v>
+      </c>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10">
+        <v>1055.2080000000001</v>
+      </c>
+      <c r="P40" s="10">
+        <v>1933.6980000000001</v>
+      </c>
+      <c r="Q40" s="147">
+        <v>1659.229</v>
+      </c>
+      <c r="R40" s="10">
+        <f t="shared" si="28"/>
+        <v>3169</v>
+      </c>
+      <c r="S40" s="15"/>
+      <c r="T40" s="10"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
+      <c r="D41" s="10">
+        <v>101</v>
+      </c>
+      <c r="E41" s="15">
+        <v>339</v>
+      </c>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
+      <c r="O41" s="10">
+        <v>146.773</v>
+      </c>
+      <c r="P41" s="10">
+        <v>299.22899999999998</v>
+      </c>
+      <c r="Q41" s="147">
+        <v>533.42899999999997</v>
+      </c>
+      <c r="R41" s="10">
+        <f t="shared" si="28"/>
+        <v>339</v>
+      </c>
+      <c r="S41" s="15"/>
       <c r="T41" s="10"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="10"/>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="10"/>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="11">
+        <f>SUM(C37:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="11">
+        <f>SUM(D37:D41)</f>
+        <v>1916</v>
+      </c>
+      <c r="E42" s="14">
+        <f>SUM(E37:E41)</f>
+        <v>7488</v>
+      </c>
+      <c r="F42" s="11">
+        <f>SUM(F37:F41)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="11">
+        <f>SUM(G37:G41)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="11">
+        <f>SUM(K37:K41)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="11">
+        <f>SUM(L37:L41)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="11">
+        <f>SUM(M37:M41)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="11">
+        <f>SUM(N37:N41)</f>
+        <v>0</v>
+      </c>
+      <c r="O42" s="11">
+        <f>SUM(O37:O41)</f>
+        <v>3102.6869999999999</v>
+      </c>
+      <c r="P42" s="11">
+        <f>SUM(P37:P41)</f>
+        <v>3945.9829999999997</v>
+      </c>
+      <c r="Q42" s="145">
+        <f>SUM(Q37:Q41)</f>
+        <v>4731.2830000000004</v>
+      </c>
+      <c r="R42" s="11">
+        <f>SUM(R37:R41)</f>
+        <v>7488</v>
+      </c>
+      <c r="S42" s="14">
+        <f>SUM(S37:S41)</f>
+        <v>0</v>
+      </c>
+      <c r="T42" s="11">
+        <f>SUM(T37:T41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
+      <c r="D43" s="10">
+        <v>637</v>
+      </c>
+      <c r="E43" s="15">
+        <v>184</v>
+      </c>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
+      <c r="O43" s="10">
+        <v>617.11</v>
+      </c>
+      <c r="P43" s="10">
+        <v>340.52699999999999</v>
+      </c>
+      <c r="Q43" s="147">
+        <v>477.51499999999999</v>
+      </c>
+      <c r="R43" s="10">
+        <f t="shared" ref="R43:R49" si="29">E43</f>
+        <v>184</v>
+      </c>
+      <c r="S43" s="15"/>
       <c r="T43" s="10"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10"/>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
+      <c r="D44" s="10">
+        <v>29</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
       <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10"/>
+      <c r="P44" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="147">
+        <v>0</v>
+      </c>
+      <c r="R44" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="15"/>
       <c r="T44" s="10"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="D45" s="10">
+        <v>11915</v>
+      </c>
+      <c r="E45" s="15">
+        <v>30557</v>
+      </c>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
+      <c r="O45" s="10">
+        <v>14210.992</v>
+      </c>
+      <c r="P45" s="10">
+        <v>16631.509999999998</v>
+      </c>
+      <c r="Q45" s="147">
+        <v>20659.181</v>
+      </c>
+      <c r="R45" s="10">
+        <f t="shared" si="29"/>
+        <v>30557</v>
+      </c>
+      <c r="S45" s="15"/>
       <c r="T45" s="10"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
+      <c r="D46" s="10">
+        <v>2590</v>
+      </c>
+      <c r="E46" s="15">
+        <v>8.2309999999999999</v>
+      </c>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
       <c r="M46" s="10"/>
       <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
+      <c r="O46" s="10">
+        <v>3063.22</v>
+      </c>
+      <c r="P46" s="10">
+        <v>3380.201</v>
+      </c>
+      <c r="Q46" s="147">
+        <v>4677.0569999999998</v>
+      </c>
+      <c r="R46" s="10">
+        <f t="shared" si="29"/>
+        <v>8.2309999999999999</v>
+      </c>
+      <c r="S46" s="15"/>
       <c r="T46" s="10"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-    </row>
-    <row r="47" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="11">
-        <f t="shared" ref="C47:D47" si="97">SUM(C41:C46)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="11">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="14">
-        <f t="shared" ref="E47:G47" si="98">SUM(E41:E46)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="11">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="11">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="11">
-        <f t="shared" ref="K47:M47" si="99">SUM(K41:K46)</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="11">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="11">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="N47" s="11">
-        <f t="shared" ref="N47:Q47" si="100">SUM(N41:N46)</f>
-        <v>0</v>
-      </c>
-      <c r="O47" s="11">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="P47" s="11">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="11">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="R47" s="11">
-        <f t="shared" ref="R47:T47" si="101">SUM(R41:R46)</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="11">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="T47" s="11">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="U47" s="14">
-        <f t="shared" ref="U47:X47" si="102">SUM(U41:U46)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="11">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="W47" s="11">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="X47" s="11">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10">
+        <v>5</v>
+      </c>
+      <c r="E47" s="15">
+        <v>235</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10">
+        <v>4.3949999999999996</v>
+      </c>
+      <c r="P47" s="10">
+        <v>205.89500000000001</v>
+      </c>
+      <c r="Q47" s="147">
+        <v>200.001</v>
+      </c>
+      <c r="R47" s="10">
+        <f t="shared" si="29"/>
+        <v>235</v>
+      </c>
+      <c r="S47" s="15"/>
+      <c r="T47" s="10"/>
+    </row>
+    <row r="48" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="15"/>
+      <c r="D48" s="10">
+        <v>20</v>
+      </c>
+      <c r="E48" s="15">
+        <v>1101</v>
+      </c>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
+      <c r="O48" s="10">
+        <v>19.544</v>
+      </c>
+      <c r="P48" s="10">
+        <v>812.97</v>
+      </c>
+      <c r="Q48" s="147">
+        <v>829.97900000000004</v>
+      </c>
+      <c r="R48" s="10">
+        <f t="shared" si="29"/>
+        <v>1101</v>
+      </c>
+      <c r="S48" s="15"/>
       <c r="T48" s="10"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
-      <c r="X48" s="10"/>
-    </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="15"/>
+      <c r="D49" s="10">
+        <v>721</v>
+      </c>
+      <c r="E49" s="15">
+        <v>1506</v>
+      </c>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
+      <c r="O49" s="10">
+        <v>842.47500000000002</v>
+      </c>
+      <c r="P49" s="10">
+        <v>924.27700000000004</v>
+      </c>
+      <c r="Q49" s="147">
+        <v>1335.482</v>
+      </c>
+      <c r="R49" s="10">
+        <f t="shared" si="29"/>
+        <v>1506</v>
+      </c>
+      <c r="S49" s="15"/>
       <c r="T49" s="10"/>
-      <c r="U49" s="15"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="X49" s="10"/>
-    </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="10"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-    </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="11">
+        <f>SUM(C42:C49)</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="11">
+        <f>SUM(D42:D49)</f>
+        <v>17833</v>
+      </c>
+      <c r="E50" s="14">
+        <f t="shared" ref="E50:G50" si="30">SUM(E42:E49)</f>
+        <v>41079.231</v>
+      </c>
+      <c r="F50" s="11">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="11">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="11">
+        <f t="shared" ref="K50:M50" si="31">SUM(K42:K49)</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="11">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="11">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="11">
+        <f t="shared" ref="N50:P50" si="32">SUM(N42:N49)</f>
+        <v>0</v>
+      </c>
+      <c r="O50" s="11">
+        <f t="shared" si="32"/>
+        <v>21860.423000000003</v>
+      </c>
+      <c r="P50" s="11">
+        <f t="shared" si="32"/>
+        <v>26241.362999999998</v>
+      </c>
+      <c r="Q50" s="145">
+        <f t="shared" ref="Q50:T50" si="33">SUM(Q42:Q49)</f>
+        <v>32910.498</v>
+      </c>
+      <c r="R50" s="11">
+        <f t="shared" si="33"/>
+        <v>41079.231</v>
+      </c>
+      <c r="S50" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="11">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="15"/>
+      <c r="D51" s="10">
+        <v>868</v>
+      </c>
+      <c r="E51" s="15">
+        <v>1623</v>
+      </c>
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
+      <c r="O51" s="10">
+        <v>1242.0999999999999</v>
+      </c>
+      <c r="P51" s="10">
+        <v>1226.579</v>
+      </c>
+      <c r="Q51" s="147">
+        <v>1156.9780000000001</v>
+      </c>
+      <c r="R51" s="10">
+        <f t="shared" ref="R51:R57" si="34">E51</f>
+        <v>1623</v>
+      </c>
+      <c r="S51" s="15"/>
       <c r="T51" s="10"/>
-      <c r="U51" s="15"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="X51" s="10"/>
-    </row>
-    <row r="52" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="15"/>
+      <c r="D52" s="10">
+        <v>356</v>
+      </c>
+      <c r="E52" s="15">
+        <v>5773</v>
+      </c>
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
       <c r="M52" s="10"/>
       <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
+      <c r="O52" s="10">
+        <v>1377.0129999999999</v>
+      </c>
+      <c r="P52" s="10">
+        <v>1411.2370000000001</v>
+      </c>
+      <c r="Q52" s="147">
+        <v>3172.2739999999999</v>
+      </c>
+      <c r="R52" s="10">
+        <f t="shared" si="34"/>
+        <v>5773</v>
+      </c>
+      <c r="S52" s="15"/>
       <c r="T52" s="10"/>
-      <c r="U52" s="15"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-    </row>
-    <row r="53" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="15"/>
+      <c r="D53" s="10">
+        <v>2468</v>
+      </c>
+      <c r="E53" s="15">
+        <v>6708</v>
+      </c>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
+      <c r="O53" s="10">
+        <v>3776.5949999999998</v>
+      </c>
+      <c r="P53" s="10">
+        <v>3627.6640000000002</v>
+      </c>
+      <c r="Q53" s="147">
+        <v>3712.1770000000001</v>
+      </c>
+      <c r="R53" s="10">
+        <f t="shared" si="34"/>
+        <v>6708</v>
+      </c>
+      <c r="S53" s="15"/>
       <c r="T53" s="10"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-    </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="11">
-        <f>SUM(C47:C53)</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="11">
-        <f>SUM(D47:D53)</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="14">
-        <f t="shared" ref="E54:G54" si="103">SUM(E47:E53)</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="11">
-        <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="11">
-        <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="11">
-        <f t="shared" ref="K54:M54" si="104">SUM(K47:K53)</f>
-        <v>0</v>
-      </c>
-      <c r="L54" s="11">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="11">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="N54" s="11">
-        <f t="shared" ref="N54:Q54" si="105">SUM(N47:N53)</f>
-        <v>0</v>
-      </c>
-      <c r="O54" s="11">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="P54" s="11">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="11">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="R54" s="11">
-        <f t="shared" ref="R54:T54" si="106">SUM(R47:R53)</f>
-        <v>0</v>
-      </c>
-      <c r="S54" s="11">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="T54" s="11">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="U54" s="14">
-        <f t="shared" ref="U54:X54" si="107">SUM(U47:U53)</f>
-        <v>0</v>
-      </c>
-      <c r="V54" s="11">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="11">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="X54" s="11">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10">
+        <v>769</v>
+      </c>
+      <c r="E54" s="15">
+        <v>1709</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10">
+        <v>436.53</v>
+      </c>
+      <c r="P54" s="10">
+        <v>951.346</v>
+      </c>
+      <c r="Q54" s="147">
+        <v>1107.58</v>
+      </c>
+      <c r="R54" s="10">
+        <f t="shared" si="34"/>
+        <v>1709</v>
+      </c>
+      <c r="S54" s="15"/>
+      <c r="T54" s="10"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="15"/>
+      <c r="D55" s="10">
+        <v>213</v>
+      </c>
+      <c r="E55" s="15">
+        <v>427</v>
+      </c>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
+      <c r="O55" s="10">
+        <v>239.54900000000001</v>
+      </c>
+      <c r="P55" s="10">
+        <v>279.08</v>
+      </c>
+      <c r="Q55" s="147">
+        <v>345.47199999999998</v>
+      </c>
+      <c r="R55" s="10">
+        <f t="shared" si="34"/>
+        <v>427</v>
+      </c>
+      <c r="S55" s="15"/>
       <c r="T55" s="10"/>
-      <c r="U55" s="15"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="10"/>
-    </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>23</v>
+        <v>180</v>
       </c>
       <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="15"/>
+      <c r="D56" s="10">
+        <v>58</v>
+      </c>
+      <c r="E56" s="15">
+        <v>38</v>
+      </c>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
       <c r="M56" s="10"/>
       <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="10"/>
-      <c r="S56" s="10"/>
+      <c r="O56" s="10">
+        <v>59.01</v>
+      </c>
+      <c r="P56" s="10">
+        <v>60.396000000000001</v>
+      </c>
+      <c r="Q56" s="147">
+        <v>48.99</v>
+      </c>
+      <c r="R56" s="10">
+        <f t="shared" si="34"/>
+        <v>38</v>
+      </c>
+      <c r="S56" s="15"/>
       <c r="T56" s="10"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-    </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="15"/>
+      <c r="D57" s="10">
+        <v>231</v>
+      </c>
+      <c r="E57" s="15">
+        <v>162</v>
+      </c>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
+      <c r="O57" s="10">
+        <v>0</v>
+      </c>
+      <c r="P57" s="10">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="Q57" s="147">
+        <v>171.40100000000001</v>
+      </c>
+      <c r="R57" s="10">
+        <f t="shared" si="34"/>
+        <v>162</v>
+      </c>
+      <c r="S57" s="15"/>
       <c r="T57" s="10"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
-      <c r="X57" s="10"/>
-    </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
-      <c r="R58" s="10"/>
-      <c r="S58" s="10"/>
-      <c r="T58" s="10"/>
-      <c r="U58" s="15"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-    </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="11">
+        <f>SUM(C51:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="11">
+        <f>SUM(D51:D57)</f>
+        <v>4963</v>
+      </c>
+      <c r="E58" s="14">
+        <f>SUM(E51:E57)</f>
+        <v>16440</v>
+      </c>
+      <c r="F58" s="11">
+        <f>SUM(F51:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="11">
+        <f>SUM(G51:G57)</f>
+        <v>0</v>
+      </c>
+      <c r="K58" s="11">
+        <f>SUM(K51:K57)</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="11">
+        <f>SUM(L51:L57)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="11">
+        <f>SUM(M51:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="11">
+        <f>SUM(N51:N57)</f>
+        <v>0</v>
+      </c>
+      <c r="O58" s="11">
+        <f>SUM(O51:O57)</f>
+        <v>7130.7969999999996</v>
+      </c>
+      <c r="P58" s="11">
+        <f>SUM(P51:P57)</f>
+        <v>7556.3549999999987</v>
+      </c>
+      <c r="Q58" s="145">
+        <f>SUM(Q51:Q57)</f>
+        <v>9714.8719999999994</v>
+      </c>
+      <c r="R58" s="11">
+        <f>SUM(R51:R57)</f>
+        <v>16440</v>
+      </c>
+      <c r="S58" s="14">
+        <f>SUM(S51:S57)</f>
+        <v>0</v>
+      </c>
+      <c r="T58" s="11">
+        <f>SUM(T51:T57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="15"/>
+      <c r="D59" s="10">
+        <v>5458</v>
+      </c>
+      <c r="E59" s="15">
+        <v>14665</v>
+      </c>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="10"/>
+      <c r="O59" s="10">
+        <v>4935.0709999999999</v>
+      </c>
+      <c r="P59" s="10">
+        <v>7423.8370000000004</v>
+      </c>
+      <c r="Q59" s="147">
+        <v>10322.757</v>
+      </c>
+      <c r="R59" s="10">
+        <f t="shared" ref="R59:R65" si="35">E59</f>
+        <v>14665</v>
+      </c>
+      <c r="S59" s="15"/>
       <c r="T59" s="10"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-    </row>
-    <row r="60" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C60" s="11">
-        <f>SUM(C55:C59)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="11">
-        <f>SUM(D55:D59)</f>
-        <v>0</v>
-      </c>
-      <c r="E60" s="14">
-        <f t="shared" ref="E60:G60" si="108">SUM(E55:E59)</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="11">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="11">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="K60" s="11">
-        <f t="shared" ref="K60:M60" si="109">SUM(K55:K59)</f>
-        <v>0</v>
-      </c>
-      <c r="L60" s="11">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="M60" s="11">
-        <f t="shared" si="109"/>
-        <v>0</v>
-      </c>
-      <c r="N60" s="11">
-        <f t="shared" ref="N60:Q60" si="110">SUM(N55:N59)</f>
-        <v>0</v>
-      </c>
-      <c r="O60" s="11">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="P60" s="11">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="11">
-        <f t="shared" si="110"/>
-        <v>0</v>
-      </c>
-      <c r="R60" s="11">
-        <f t="shared" ref="R60:T60" si="111">SUM(R55:R59)</f>
-        <v>0</v>
-      </c>
-      <c r="S60" s="11">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="T60" s="11">
-        <f t="shared" si="111"/>
-        <v>0</v>
-      </c>
-      <c r="U60" s="14">
-        <f t="shared" ref="U60:X60" si="112">SUM(U55:U59)</f>
-        <v>0</v>
-      </c>
-      <c r="V60" s="11">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="W60" s="11">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-      <c r="X60" s="11">
-        <f t="shared" si="112"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10">
+        <v>200</v>
+      </c>
+      <c r="E60" s="15">
+        <v>1</v>
+      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="P60" s="10">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="Q60" s="147">
+        <v>1.71</v>
+      </c>
+      <c r="R60" s="10">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="S60" s="15"/>
+      <c r="T60" s="10"/>
+    </row>
+    <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="15"/>
+      <c r="D61" s="10">
+        <v>3295</v>
+      </c>
+      <c r="E61" s="15">
+        <v>6476</v>
+      </c>
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
+      <c r="O61" s="10">
+        <v>3611.4690000000001</v>
+      </c>
+      <c r="P61" s="10">
+        <v>3896.1729999999998</v>
+      </c>
+      <c r="Q61" s="147">
+        <v>4228.2219999999998</v>
+      </c>
+      <c r="R61" s="10">
+        <f t="shared" si="35"/>
+        <v>6476</v>
+      </c>
+      <c r="S61" s="15"/>
       <c r="T61" s="10"/>
-      <c r="U61" s="15"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-    </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="15"/>
+      <c r="D62" s="10">
+        <v>2389</v>
+      </c>
+      <c r="E62" s="15">
+        <v>7768</v>
+      </c>
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="10"/>
-      <c r="S62" s="10"/>
+      <c r="O62" s="10">
+        <v>2867.8380000000002</v>
+      </c>
+      <c r="P62" s="10">
+        <v>3168.3919999999998</v>
+      </c>
+      <c r="Q62" s="147">
+        <v>4378.8689999999997</v>
+      </c>
+      <c r="R62" s="10">
+        <f t="shared" si="35"/>
+        <v>7768</v>
+      </c>
+      <c r="S62" s="15"/>
       <c r="T62" s="10"/>
-      <c r="U62" s="15"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-    </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="15"/>
+      <c r="D63" s="10">
+        <v>34</v>
+      </c>
+      <c r="E63" s="15">
+        <v>216</v>
+      </c>
       <c r="F63" s="10"/>
       <c r="G63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
+      <c r="O63" s="10">
+        <v>18.814</v>
+      </c>
+      <c r="P63" s="10">
+        <v>3.1120000000000001</v>
+      </c>
+      <c r="Q63" s="147">
+        <v>12</v>
+      </c>
+      <c r="R63" s="10">
+        <f t="shared" si="35"/>
+        <v>216</v>
+      </c>
+      <c r="S63" s="15"/>
       <c r="T63" s="10"/>
-      <c r="U63" s="15"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
-      <c r="X63" s="10"/>
-    </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="15"/>
+      <c r="D64" s="10">
+        <v>149</v>
+      </c>
+      <c r="E64" s="15">
+        <v>115</v>
+      </c>
       <c r="F64" s="10"/>
       <c r="G64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
       <c r="M64" s="10"/>
       <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="10"/>
+      <c r="O64" s="10">
+        <v>193.84899999999999</v>
+      </c>
+      <c r="P64" s="10">
+        <v>245.65899999999999</v>
+      </c>
+      <c r="Q64" s="147">
+        <v>117.633</v>
+      </c>
+      <c r="R64" s="10">
+        <f t="shared" si="35"/>
+        <v>115</v>
+      </c>
+      <c r="S64" s="15"/>
       <c r="T64" s="10"/>
-      <c r="U64" s="15"/>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
-      <c r="X64" s="10"/>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C65" s="11">
-        <f>SUM(C60:C64)</f>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10">
+        <v>37</v>
+      </c>
+      <c r="E65" s="15">
+        <v>286</v>
+      </c>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="P65" s="10">
+        <v>126.331</v>
+      </c>
+      <c r="Q65" s="147">
+        <v>268.40899999999999</v>
+      </c>
+      <c r="R65" s="10">
+        <f t="shared" si="35"/>
+        <v>286</v>
+      </c>
+      <c r="S65" s="15"/>
+      <c r="T65" s="10"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="11">
+        <f>SUM(C58:C65)</f>
         <v>0</v>
       </c>
-      <c r="D65" s="11">
-        <f>SUM(D60:D64)</f>
+      <c r="D66" s="11">
+        <f>SUM(D58:D65)</f>
+        <v>16525</v>
+      </c>
+      <c r="E66" s="14">
+        <f t="shared" ref="E66:G66" si="36">SUM(E58:E65)</f>
+        <v>45967</v>
+      </c>
+      <c r="F66" s="11">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="E65" s="14">
-        <f t="shared" ref="E65:G65" si="113">SUM(E60:E64)</f>
+      <c r="G66" s="11">
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="F65" s="11">
-        <f t="shared" si="113"/>
+      <c r="K66" s="11">
+        <f t="shared" ref="K66:M66" si="37">SUM(K58:K65)</f>
         <v>0</v>
       </c>
-      <c r="G65" s="11">
-        <f t="shared" si="113"/>
+      <c r="L66" s="11">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="K65" s="11">
-        <f t="shared" ref="K65:M65" si="114">SUM(K60:K64)</f>
+      <c r="M66" s="11">
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="L65" s="11">
-        <f t="shared" si="114"/>
+      <c r="N66" s="11">
+        <f t="shared" ref="N66:P66" si="38">SUM(N58:N65)</f>
         <v>0</v>
       </c>
-      <c r="M65" s="11">
-        <f t="shared" si="114"/>
+      <c r="O66" s="11">
+        <f t="shared" si="38"/>
+        <v>18791.100999999995</v>
+      </c>
+      <c r="P66" s="11">
+        <f t="shared" si="38"/>
+        <v>22420.556999999997</v>
+      </c>
+      <c r="Q66" s="145">
+        <f t="shared" ref="Q66:T66" si="39">SUM(Q58:Q65)</f>
+        <v>29044.472000000002</v>
+      </c>
+      <c r="R66" s="11">
+        <f>SUM(R58:R65)</f>
+        <v>45967</v>
+      </c>
+      <c r="S66" s="14">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N65" s="11">
-        <f t="shared" ref="N65:Q65" si="115">SUM(N60:N64)</f>
+      <c r="T66" s="11">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O65" s="11">
-        <f t="shared" si="115"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="10">
+        <f>C50-C66</f>
         <v>0</v>
       </c>
-      <c r="P65" s="11">
-        <f t="shared" si="115"/>
+      <c r="D67" s="10">
+        <f>D50-D66</f>
+        <v>1308</v>
+      </c>
+      <c r="E67" s="15">
+        <f>E50-E66</f>
+        <v>-4887.7690000000002</v>
+      </c>
+      <c r="F67" s="10">
+        <f>F50-F66</f>
         <v>0</v>
       </c>
-      <c r="Q65" s="11">
-        <f t="shared" si="115"/>
+      <c r="G67" s="10">
+        <f>G50-G66</f>
         <v>0</v>
       </c>
-      <c r="R65" s="11">
-        <f t="shared" ref="R65:T65" si="116">SUM(R60:R64)</f>
+      <c r="K67" s="10">
+        <f>K50-K66</f>
         <v>0</v>
       </c>
-      <c r="S65" s="11">
-        <f t="shared" si="116"/>
+      <c r="L67" s="10">
+        <f>L50-L66</f>
         <v>0</v>
       </c>
-      <c r="T65" s="11">
-        <f t="shared" si="116"/>
+      <c r="M67" s="10">
+        <f>M50-M66</f>
         <v>0</v>
       </c>
-      <c r="U65" s="14">
-        <f t="shared" ref="U65:X65" si="117">SUM(U60:U64)</f>
+      <c r="N67" s="10">
+        <f>N50-N66</f>
         <v>0</v>
       </c>
-      <c r="V65" s="11">
-        <f t="shared" si="117"/>
+      <c r="O67" s="10">
+        <f>O50-O66</f>
+        <v>3069.3220000000074</v>
+      </c>
+      <c r="P67" s="10">
+        <f>P50-P66</f>
+        <v>3820.8060000000005</v>
+      </c>
+      <c r="Q67" s="147">
+        <f>Q50-Q66</f>
+        <v>3866.025999999998</v>
+      </c>
+      <c r="R67" s="10">
+        <f>R50-R66</f>
+        <v>-4887.7690000000002</v>
+      </c>
+      <c r="S67" s="15">
+        <f>S50-S66</f>
         <v>0</v>
       </c>
-      <c r="W65" s="11">
-        <f t="shared" si="117"/>
+      <c r="T67" s="10">
+        <f>T50-T66</f>
         <v>0</v>
       </c>
-      <c r="X65" s="11">
-        <f t="shared" si="117"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" s="10">
-        <f>C54-C65</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="10">
-        <f>D54-D65</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="15">
-        <f t="shared" ref="E66:G66" si="118">E54-E65</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="10">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="G66" s="10">
-        <f t="shared" si="118"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="10">
-        <f t="shared" ref="K66:M66" si="119">K54-K65</f>
-        <v>0</v>
-      </c>
-      <c r="L66" s="10">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-      <c r="M66" s="10">
-        <f t="shared" si="119"/>
-        <v>0</v>
-      </c>
-      <c r="N66" s="10">
-        <f t="shared" ref="N66:Q66" si="120">N54-N65</f>
-        <v>0</v>
-      </c>
-      <c r="O66" s="10">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="10">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="10">
-        <f t="shared" si="120"/>
-        <v>0</v>
-      </c>
-      <c r="R66" s="10">
-        <f t="shared" ref="R66:T66" si="121">R54-R65</f>
-        <v>0</v>
-      </c>
-      <c r="S66" s="10">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="T66" s="10">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="U66" s="15">
-        <f t="shared" ref="U66:X66" si="122">U54-U65</f>
-        <v>0</v>
-      </c>
-      <c r="V66" s="10">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-      <c r="W66" s="10">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-      <c r="X66" s="10">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" s="50"/>
-      <c r="D68" s="122"/>
-      <c r="E68" s="16"/>
-      <c r="U68" s="16"/>
-    </row>
-    <row r="86" spans="5:21" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="41"/>
-      <c r="U86" s="41"/>
-    </row>
-    <row r="87" spans="5:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="16"/>
-      <c r="U87" s="16"/>
+    </row>
+    <row r="69" spans="2:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="46"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="16"/>
+      <c r="Q69" s="150"/>
+      <c r="S69" s="16"/>
+    </row>
+    <row r="87" spans="5:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E87" s="40"/>
+      <c r="Q87" s="151"/>
+      <c r="S87" s="40"/>
+    </row>
+    <row r="88" spans="5:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E88" s="16"/>
+      <c r="Q88" s="150"/>
+      <c r="S88" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -18914,73 +19237,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="120">
+      <c r="B1" s="116">
         <v>45413</v>
       </c>
-      <c r="C1" s="120">
+      <c r="C1" s="116">
         <v>45444</v>
       </c>
-      <c r="D1" s="120">
+      <c r="D1" s="116">
         <v>45474</v>
       </c>
-      <c r="E1" s="120">
+      <c r="E1" s="116">
         <v>45505</v>
       </c>
-      <c r="F1" s="120">
+      <c r="F1" s="116">
         <v>45536</v>
       </c>
-      <c r="G1" s="120">
+      <c r="G1" s="116">
         <v>45566</v>
       </c>
-      <c r="H1" s="120">
+      <c r="H1" s="116">
         <v>45597</v>
       </c>
-      <c r="I1" s="120">
+      <c r="I1" s="116">
         <v>45627</v>
       </c>
-      <c r="J1" s="120">
+      <c r="J1" s="116">
         <v>45658</v>
       </c>
-      <c r="K1" s="120">
+      <c r="K1" s="116">
         <v>45689</v>
       </c>
-      <c r="L1" s="120">
+      <c r="L1" s="116">
         <v>45717</v>
       </c>
-      <c r="M1" s="120">
+      <c r="M1" s="116">
         <v>45748</v>
       </c>
-      <c r="N1" s="120">
+      <c r="N1" s="116">
         <v>45778</v>
       </c>
-      <c r="O1" s="120">
+      <c r="O1" s="116">
         <v>45809</v>
       </c>
-      <c r="P1" s="120">
+      <c r="P1" s="116">
         <v>45839</v>
       </c>
-      <c r="Q1" s="120">
+      <c r="Q1" s="116">
         <v>45870</v>
       </c>
-      <c r="R1" s="120">
+      <c r="R1" s="116">
         <v>45901</v>
       </c>
-      <c r="S1" s="120">
+      <c r="S1" s="116">
         <v>45931</v>
       </c>
-      <c r="T1" s="120">
+      <c r="T1" s="116">
         <v>45962</v>
       </c>
-      <c r="U1" s="120">
+      <c r="U1" s="116">
         <v>45992</v>
       </c>
-      <c r="V1" s="120">
+      <c r="V1" s="116">
         <v>46023</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -18994,7 +19317,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I3">
         <v>3</v>
@@ -19008,7 +19331,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -19022,7 +19345,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -19036,12 +19359,12 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="I9">
         <v>80</v>
@@ -19055,7 +19378,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="I10">
         <v>90</v>
@@ -19069,7 +19392,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="I11">
         <v>40</v>
@@ -19094,7 +19417,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -19112,6 +19435,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19132,26 +19456,26 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" s="12"/>
       <c r="C2" s="18"/>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -19161,7 +19485,7 @@
         <v>45328</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M3" s="12"/>
     </row>
@@ -19172,7 +19496,7 @@
         <v>45302</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -27462,60 +27786,60 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="134" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="136"/>
+        <v>77</v>
+      </c>
+      <c r="H1" s="130" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="132"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" t="e">
         <f>C2/C3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H2" s="56"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="58"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D3" t="e">
         <f t="shared" ref="D3:D66" si="0">C3/C4-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H3" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="L3" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="M3" s="63" t="s">
-        <v>108</v>
+      <c r="H3" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="59" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -27523,27 +27847,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H4" s="64" t="e">
+      <c r="H4" s="60" t="e">
         <f>$I$19-3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I4" s="65" t="e">
+      <c r="I4" s="61" t="e">
         <f>H4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J4" s="66">
+      <c r="J4" s="62">
         <f>COUNTIF(D:D,"&lt;="&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K4" s="66" t="e">
+      <c r="K4" s="62" t="e">
         <f>"Less than "&amp;TEXT(H4,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L4" s="67" t="e">
+      <c r="L4" s="63" t="e">
         <f>J4/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M4" s="68" t="e">
+      <c r="M4" s="64" t="e">
         <f>L4</f>
         <v>#DIV/0!</v>
       </c>
@@ -27553,27 +27877,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="69" t="e">
+      <c r="H5" s="65" t="e">
         <f>$I$19-2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I5" s="70" t="e">
+      <c r="I5" s="66" t="e">
         <f>H5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="71">
+      <c r="J5" s="67">
         <f>COUNTIFS(D:D,"&lt;="&amp;H5,D:D,"&gt;"&amp;H4)</f>
         <v>67</v>
       </c>
-      <c r="K5" s="72" t="e">
+      <c r="K5" s="68" t="e">
         <f t="shared" ref="K5:K14" si="1">TEXT(H4,"0,00%")&amp;" to "&amp;TEXT(H5,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L5" s="73" t="e">
+      <c r="L5" s="69" t="e">
         <f>J5/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M5" s="74" t="e">
+      <c r="M5" s="70" t="e">
         <f>M4+L5</f>
         <v>#DIV/0!</v>
       </c>
@@ -27583,27 +27907,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="69" t="e">
+      <c r="H6" s="65" t="e">
         <f>$I$19-1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I6" s="70" t="e">
+      <c r="I6" s="66" t="e">
         <f t="shared" ref="I6:I14" si="2">H6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J6" s="71">
+      <c r="J6" s="67">
         <f t="shared" ref="J6:J14" si="3">COUNTIFS(D:D,"&lt;="&amp;H6,D:D,"&gt;"&amp;H5)</f>
         <v>67</v>
       </c>
-      <c r="K6" s="72" t="e">
+      <c r="K6" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="73" t="e">
+      <c r="L6" s="69" t="e">
         <f t="shared" ref="L6:L15" si="4">J6/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M6" s="74" t="e">
+      <c r="M6" s="70" t="e">
         <f t="shared" ref="M6:M15" si="5">M5+L6</f>
         <v>#DIV/0!</v>
       </c>
@@ -27613,27 +27937,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="69" t="e">
+      <c r="H7" s="65" t="e">
         <f>$I$19-1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I7" s="70" t="e">
+      <c r="I7" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K7" s="72" t="e">
+      <c r="K7" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L7" s="73" t="e">
+      <c r="L7" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M7" s="74" t="e">
+      <c r="M7" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27643,27 +27967,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="69" t="e">
+      <c r="H8" s="65" t="e">
         <f>$I$19-0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8" s="70" t="e">
+      <c r="I8" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K8" s="72" t="e">
+      <c r="K8" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L8" s="73" t="e">
+      <c r="L8" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M8" s="74" t="e">
+      <c r="M8" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27673,27 +27997,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="69" t="e">
+      <c r="H9" s="65" t="e">
         <f>$I$19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="70" t="e">
+      <c r="I9" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="71">
+      <c r="J9" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K9" s="72" t="e">
+      <c r="K9" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L9" s="73" t="e">
+      <c r="L9" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="74" t="e">
+      <c r="M9" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27703,27 +28027,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="69" t="e">
+      <c r="H10" s="65" t="e">
         <f>$I$19+0.6*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="70" t="e">
+      <c r="I10" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="71">
+      <c r="J10" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K10" s="72" t="e">
+      <c r="K10" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L10" s="73" t="e">
+      <c r="L10" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="74" t="e">
+      <c r="M10" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27733,27 +28057,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H11" s="69" t="e">
+      <c r="H11" s="65" t="e">
         <f>$I$19+1.2*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="70" t="e">
+      <c r="I11" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="71">
+      <c r="J11" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K11" s="72" t="e">
+      <c r="K11" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L11" s="73" t="e">
+      <c r="L11" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M11" s="74" t="e">
+      <c r="M11" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27763,27 +28087,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H12" s="69" t="e">
+      <c r="H12" s="65" t="e">
         <f>$I$19+1.8*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="70" t="e">
+      <c r="I12" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J12" s="71">
+      <c r="J12" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K12" s="72" t="e">
+      <c r="K12" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L12" s="73" t="e">
+      <c r="L12" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M12" s="74" t="e">
+      <c r="M12" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27793,27 +28117,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H13" s="69" t="e">
+      <c r="H13" s="65" t="e">
         <f>$I$19+2.4*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13" s="70" t="e">
+      <c r="I13" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J13" s="71">
+      <c r="J13" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K13" s="72" t="e">
+      <c r="K13" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L13" s="73" t="e">
+      <c r="L13" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M13" s="74" t="e">
+      <c r="M13" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27823,27 +28147,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H14" s="69" t="e">
+      <c r="H14" s="65" t="e">
         <f>$I$19+3*$I$23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14" s="70" t="e">
+      <c r="I14" s="66" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="71">
+      <c r="J14" s="67">
         <f t="shared" si="3"/>
         <v>67</v>
       </c>
-      <c r="K14" s="72" t="e">
+      <c r="K14" s="68" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L14" s="73" t="e">
+      <c r="L14" s="69" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M14" s="74" t="e">
+      <c r="M14" s="70" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27853,23 +28177,23 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H15" s="75"/>
-      <c r="I15" s="76" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="76">
+      <c r="H15" s="71"/>
+      <c r="I15" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="J15" s="72">
         <f>COUNTIF(D:D,"&gt;"&amp;H14)</f>
         <v>67</v>
       </c>
-      <c r="K15" s="76" t="e">
+      <c r="K15" s="72" t="e">
         <f>"Greater than "&amp;TEXT(H14,"0,00%")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L15" s="77" t="e">
+      <c r="L15" s="73" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M15" s="77" t="e">
+      <c r="M15" s="73" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -27879,350 +28203,350 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H16" s="78"/>
-      <c r="M16" s="79"/>
+      <c r="H16" s="74"/>
+      <c r="M16" s="75"/>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H17" s="137" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="138"/>
-      <c r="M17" s="79"/>
+      <c r="H17" s="133" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="134"/>
+      <c r="M17" s="75"/>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H18" s="139"/>
-      <c r="I18" s="140"/>
-      <c r="M18" s="79"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="136"/>
+      <c r="M18" s="75"/>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H19" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" s="116" t="e">
+      <c r="H19" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="112" t="e">
         <f>AVERAGE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M19" s="79"/>
+      <c r="M19" s="75"/>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="80" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="116" t="e">
+      <c r="H20" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="112" t="e">
         <f>_xlfn.STDEV.S(D:D)/SQRT(COUNT(D:D))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M20" s="79"/>
+      <c r="M20" s="75"/>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D21" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" s="80" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="116" t="e">
+      <c r="H21" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="112" t="e">
         <f>MEDIAN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M21" s="79"/>
+      <c r="M21" s="75"/>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" s="80" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="116" t="e">
+      <c r="H22" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="112" t="e">
         <f>MODE(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M22" s="79"/>
+      <c r="M22" s="75"/>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" s="80" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="116" t="e">
+      <c r="H23" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="112" t="e">
         <f>_xlfn.STDEV.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M23" s="79"/>
+      <c r="M23" s="75"/>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D24" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" s="80" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24" s="116" t="e">
+      <c r="H24" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="112" t="e">
         <f>_xlfn.VAR.S(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M24" s="79"/>
+      <c r="M24" s="75"/>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D25" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" s="80" t="s">
-        <v>116</v>
-      </c>
-      <c r="I25" s="117" t="e">
+      <c r="H25" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="113" t="e">
         <f>KURT(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M25" s="79"/>
+      <c r="M25" s="75"/>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D26" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="80" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="117" t="e">
+      <c r="H26" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="113" t="e">
         <f>SKEW(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M26" s="79"/>
+      <c r="M26" s="75"/>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D27" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H27" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="116" t="e">
+      <c r="H27" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="112" t="e">
         <f>I29-I28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M27" s="79"/>
+      <c r="M27" s="75"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" s="116" t="e">
+      <c r="H28" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="112" t="e">
         <f>MIN(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M28" s="79"/>
+      <c r="M28" s="75"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="80" t="s">
-        <v>119</v>
-      </c>
-      <c r="I29" s="116" t="e">
+      <c r="H29" s="76" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="112" t="e">
         <f>MAX(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M29" s="79"/>
+      <c r="M29" s="75"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H30" s="80" t="s">
-        <v>120</v>
-      </c>
-      <c r="I30" s="117" t="e">
+      <c r="H30" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="I30" s="113" t="e">
         <f>SUM(D:D)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="79"/>
+      <c r="M30" s="75"/>
     </row>
     <row r="31" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D31" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="I31" s="58">
+      <c r="H31" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="54">
         <f>COUNT(D:D)</f>
         <v>0</v>
       </c>
-      <c r="M31" s="79"/>
+      <c r="M31" s="75"/>
     </row>
     <row r="32" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D32" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H32" s="83"/>
-      <c r="M32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="M32" s="75"/>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D33" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" s="84"/>
-      <c r="I33" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="J33" s="85" t="s">
-        <v>121</v>
-      </c>
-      <c r="K33" s="85" t="s">
-        <v>123</v>
-      </c>
-      <c r="L33" s="86" t="s">
-        <v>124</v>
-      </c>
-      <c r="M33" s="79"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="J33" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="K33" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="M33" s="75"/>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D34" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H34" s="87" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="73" t="e">
+      <c r="H34" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="I34" s="69" t="e">
         <f>AVERAGEIF(D:D,"&gt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" s="71">
+      <c r="J34" s="67">
         <f>COUNTIF(D:D,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="K34" s="73" t="e">
+      <c r="K34" s="69" t="e">
         <f>J34/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L34" s="74" t="e">
+      <c r="L34" s="70" t="e">
         <f>K34*I34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M34" s="79"/>
+      <c r="M34" s="75"/>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D35" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="87" t="s">
-        <v>126</v>
-      </c>
-      <c r="I35" s="73" t="e">
+      <c r="H35" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="69" t="e">
         <f>AVERAGEIF(D:D,"&lt;0")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J35" s="71">
+      <c r="J35" s="67">
         <f>COUNTIF(D:D,"&lt;0")</f>
         <v>0</v>
       </c>
-      <c r="K35" s="73" t="e">
+      <c r="K35" s="69" t="e">
         <f>J35/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L35" s="74" t="e">
+      <c r="L35" s="70" t="e">
         <f t="shared" ref="L35:L36" si="6">K35*I35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M35" s="79"/>
+      <c r="M35" s="75"/>
     </row>
     <row r="36" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D36" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H36" s="88" t="s">
-        <v>127</v>
-      </c>
-      <c r="I36" s="76">
+      <c r="H36" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" s="72">
         <v>0</v>
       </c>
-      <c r="J36" s="76">
+      <c r="J36" s="72">
         <f>COUNTIF(D:D,"0")</f>
         <v>0</v>
       </c>
-      <c r="K36" s="89" t="e">
+      <c r="K36" s="85" t="e">
         <f>J36/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L36" s="77" t="e">
+      <c r="L36" s="73" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M36" s="79"/>
+      <c r="M36" s="75"/>
     </row>
     <row r="37" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D37" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H37" s="83"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="90"/>
-      <c r="K37" s="90"/>
-      <c r="L37" s="90"/>
-      <c r="M37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="75"/>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D38" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H38" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="I38" s="85" t="s">
-        <v>129</v>
-      </c>
-      <c r="J38" s="85" t="s">
-        <v>130</v>
-      </c>
-      <c r="K38" s="85" t="s">
-        <v>131</v>
-      </c>
-      <c r="L38" s="85" t="s">
-        <v>132</v>
-      </c>
-      <c r="M38" s="86" t="s">
-        <v>133</v>
+      <c r="H38" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="K38" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="L38" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="M38" s="82" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.25">
@@ -28230,26 +28554,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H39" s="91">
+      <c r="H39" s="87">
         <v>1</v>
       </c>
-      <c r="I39" s="73" t="e">
+      <c r="I39" s="69" t="e">
         <f>$I$19+($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J39" s="73" t="e">
+      <c r="J39" s="69" t="e">
         <f>$I$19-($H39*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K39" s="71">
+      <c r="K39" s="67">
         <f>COUNTIFS(D:D,"&lt;"&amp;I39,D:D,"&gt;"&amp;J39)</f>
         <v>67</v>
       </c>
-      <c r="L39" s="73" t="e">
+      <c r="L39" s="69" t="e">
         <f>K39/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M39" s="74">
+      <c r="M39" s="70">
         <v>0.68269999999999997</v>
       </c>
     </row>
@@ -28258,26 +28582,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="91">
+      <c r="H40" s="87">
         <v>2</v>
       </c>
-      <c r="I40" s="73" t="e">
+      <c r="I40" s="69" t="e">
         <f>$I$19+($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J40" s="73" t="e">
+      <c r="J40" s="69" t="e">
         <f>$I$19-($H40*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K40" s="71">
+      <c r="K40" s="67">
         <f>COUNTIFS(D:D,"&lt;"&amp;I40,D:D,"&gt;"&amp;J40)</f>
         <v>67</v>
       </c>
-      <c r="L40" s="73" t="e">
+      <c r="L40" s="69" t="e">
         <f>K40/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M40" s="74">
+      <c r="M40" s="70">
         <v>0.95450000000000002</v>
       </c>
     </row>
@@ -28286,26 +28610,26 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="91">
+      <c r="H41" s="87">
         <v>3</v>
       </c>
-      <c r="I41" s="73" t="e">
+      <c r="I41" s="69" t="e">
         <f>$I$19+($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="73" t="e">
+      <c r="J41" s="69" t="e">
         <f>$I$19-($H41*$I$23)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K41" s="71">
+      <c r="K41" s="67">
         <f>COUNTIFS(D:D,"&lt;"&amp;I41,D:D,"&gt;"&amp;J41)</f>
         <v>67</v>
       </c>
-      <c r="L41" s="73" t="e">
+      <c r="L41" s="69" t="e">
         <f>K41/$I$31</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M41" s="92">
+      <c r="M41" s="88">
         <v>0.99729999999999996</v>
       </c>
     </row>
@@ -28314,46 +28638,46 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H42" s="69"/>
-      <c r="M42" s="92"/>
+      <c r="H42" s="65"/>
+      <c r="M42" s="88"/>
     </row>
     <row r="43" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D43" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H43" s="141" t="s">
-        <v>134</v>
-      </c>
-      <c r="I43" s="142"/>
-      <c r="J43" s="142"/>
-      <c r="K43" s="142"/>
-      <c r="L43" s="142"/>
-      <c r="M43" s="143"/>
+      <c r="H43" s="137" t="s">
+        <v>110</v>
+      </c>
+      <c r="I43" s="138"/>
+      <c r="J43" s="138"/>
+      <c r="K43" s="138"/>
+      <c r="L43" s="138"/>
+      <c r="M43" s="139"/>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D44" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H44" s="93">
+      <c r="H44" s="89">
         <v>0.01</v>
       </c>
-      <c r="I44" s="94" t="e">
+      <c r="I44" s="90" t="e">
         <f t="shared" ref="I44:I58" si="7">_xlfn.PERCENTILE.INC(D:D,H44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J44" s="95">
+      <c r="J44" s="91">
         <v>0.2</v>
       </c>
-      <c r="K44" s="94" t="e">
+      <c r="K44" s="90" t="e">
         <f t="shared" ref="K44:K56" si="8">_xlfn.PERCENTILE.INC(D:D,J44)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L44" s="95">
+      <c r="L44" s="91">
         <v>0.85</v>
       </c>
-      <c r="M44" s="96" t="e">
+      <c r="M44" s="92" t="e">
         <f t="shared" ref="M44:M58" si="9">_xlfn.PERCENTILE.INC(D:D,L44)</f>
         <v>#DIV/0!</v>
       </c>
@@ -28363,24 +28687,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H45" s="97">
+      <c r="H45" s="93">
         <v>0.02</v>
       </c>
-      <c r="I45" s="98" t="e">
+      <c r="I45" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J45" s="99">
+      <c r="J45" s="95">
         <v>0.25</v>
       </c>
-      <c r="K45" s="98" t="e">
+      <c r="K45" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L45" s="99">
+      <c r="L45" s="95">
         <v>0.86</v>
       </c>
-      <c r="M45" s="100" t="e">
+      <c r="M45" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28390,24 +28714,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H46" s="97">
+      <c r="H46" s="93">
         <v>0.03</v>
       </c>
-      <c r="I46" s="98" t="e">
+      <c r="I46" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J46" s="99">
+      <c r="J46" s="95">
         <v>0.3</v>
       </c>
-      <c r="K46" s="98" t="e">
+      <c r="K46" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L46" s="99">
+      <c r="L46" s="95">
         <v>0.87</v>
       </c>
-      <c r="M46" s="100" t="e">
+      <c r="M46" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28417,24 +28741,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H47" s="97">
+      <c r="H47" s="93">
         <v>0.04</v>
       </c>
-      <c r="I47" s="98" t="e">
+      <c r="I47" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J47" s="99">
+      <c r="J47" s="95">
         <v>0.35</v>
       </c>
-      <c r="K47" s="98" t="e">
+      <c r="K47" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L47" s="99">
+      <c r="L47" s="95">
         <v>0.88</v>
       </c>
-      <c r="M47" s="100" t="e">
+      <c r="M47" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28444,24 +28768,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H48" s="97">
+      <c r="H48" s="93">
         <v>0.05</v>
       </c>
-      <c r="I48" s="98" t="e">
+      <c r="I48" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J48" s="99">
+      <c r="J48" s="95">
         <v>0.4</v>
       </c>
-      <c r="K48" s="98" t="e">
+      <c r="K48" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L48" s="99">
+      <c r="L48" s="95">
         <v>0.89</v>
       </c>
-      <c r="M48" s="100" t="e">
+      <c r="M48" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28471,24 +28795,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H49" s="97">
+      <c r="H49" s="93">
         <v>0.06</v>
       </c>
-      <c r="I49" s="98" t="e">
+      <c r="I49" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J49" s="99">
+      <c r="J49" s="95">
         <v>0.45</v>
       </c>
-      <c r="K49" s="98" t="e">
+      <c r="K49" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L49" s="99">
+      <c r="L49" s="95">
         <v>0.9</v>
       </c>
-      <c r="M49" s="100" t="e">
+      <c r="M49" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28498,24 +28822,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H50" s="97">
+      <c r="H50" s="93">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I50" s="98" t="e">
+      <c r="I50" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J50" s="99">
+      <c r="J50" s="95">
         <v>0.5</v>
       </c>
-      <c r="K50" s="98" t="e">
+      <c r="K50" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L50" s="99">
+      <c r="L50" s="95">
         <v>0.91</v>
       </c>
-      <c r="M50" s="100" t="e">
+      <c r="M50" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28525,24 +28849,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H51" s="97">
+      <c r="H51" s="93">
         <v>0.08</v>
       </c>
-      <c r="I51" s="98" t="e">
+      <c r="I51" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J51" s="99">
+      <c r="J51" s="95">
         <v>0.55000000000000004</v>
       </c>
-      <c r="K51" s="98" t="e">
+      <c r="K51" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L51" s="99">
+      <c r="L51" s="95">
         <v>0.92</v>
       </c>
-      <c r="M51" s="100" t="e">
+      <c r="M51" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28552,24 +28876,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H52" s="97">
+      <c r="H52" s="93">
         <v>0.09</v>
       </c>
-      <c r="I52" s="98" t="e">
+      <c r="I52" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J52" s="99">
+      <c r="J52" s="95">
         <v>0.6</v>
       </c>
-      <c r="K52" s="98" t="e">
+      <c r="K52" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L52" s="99">
+      <c r="L52" s="95">
         <v>0.93</v>
       </c>
-      <c r="M52" s="100" t="e">
+      <c r="M52" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28579,24 +28903,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H53" s="97">
+      <c r="H53" s="93">
         <v>0.1</v>
       </c>
-      <c r="I53" s="98" t="e">
+      <c r="I53" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J53" s="99">
+      <c r="J53" s="95">
         <v>0.65</v>
       </c>
-      <c r="K53" s="98" t="e">
+      <c r="K53" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L53" s="99">
+      <c r="L53" s="95">
         <v>0.94</v>
       </c>
-      <c r="M53" s="100" t="e">
+      <c r="M53" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28606,24 +28930,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H54" s="97">
+      <c r="H54" s="93">
         <v>0.11</v>
       </c>
-      <c r="I54" s="98" t="e">
+      <c r="I54" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="99">
+      <c r="J54" s="95">
         <v>0.7</v>
       </c>
-      <c r="K54" s="98" t="e">
+      <c r="K54" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L54" s="99">
+      <c r="L54" s="95">
         <v>0.95</v>
       </c>
-      <c r="M54" s="100" t="e">
+      <c r="M54" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28633,24 +28957,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H55" s="97">
+      <c r="H55" s="93">
         <v>0.12</v>
       </c>
-      <c r="I55" s="98" t="e">
+      <c r="I55" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J55" s="99">
+      <c r="J55" s="95">
         <v>0.75</v>
       </c>
-      <c r="K55" s="98" t="e">
+      <c r="K55" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="99">
+      <c r="L55" s="95">
         <v>0.96</v>
       </c>
-      <c r="M55" s="100" t="e">
+      <c r="M55" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28660,24 +28984,24 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="97">
+      <c r="H56" s="93">
         <v>0.13</v>
       </c>
-      <c r="I56" s="98" t="e">
+      <c r="I56" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J56" s="99">
+      <c r="J56" s="95">
         <v>0.8</v>
       </c>
-      <c r="K56" s="98" t="e">
+      <c r="K56" s="94" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L56" s="99">
+      <c r="L56" s="95">
         <v>0.97</v>
       </c>
-      <c r="M56" s="100" t="e">
+      <c r="M56" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28687,19 +29011,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H57" s="97">
+      <c r="H57" s="93">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I57" s="98" t="e">
+      <c r="I57" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J57" s="99"/>
-      <c r="K57" s="98"/>
-      <c r="L57" s="99">
+      <c r="J57" s="95"/>
+      <c r="K57" s="94"/>
+      <c r="L57" s="95">
         <v>0.98</v>
       </c>
-      <c r="M57" s="100" t="e">
+      <c r="M57" s="96" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28709,19 +29033,19 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H58" s="101">
+      <c r="H58" s="97">
         <v>0.15</v>
       </c>
-      <c r="I58" s="102" t="e">
+      <c r="I58" s="98" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J58" s="103"/>
-      <c r="K58" s="82"/>
-      <c r="L58" s="104">
+      <c r="J58" s="99"/>
+      <c r="K58" s="78"/>
+      <c r="L58" s="100">
         <v>0.99</v>
       </c>
-      <c r="M58" s="105" t="e">
+      <c r="M58" s="101" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
@@ -28737,47 +29061,47 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H60" s="106" t="s">
-        <v>135</v>
-      </c>
-      <c r="I60" s="107"/>
+      <c r="H60" s="102" t="s">
+        <v>111</v>
+      </c>
+      <c r="I60" s="103"/>
     </row>
     <row r="61" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D61" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H61" s="108" t="s">
-        <v>136</v>
-      </c>
-      <c r="I61" s="109"/>
+      <c r="H61" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="I61" s="105"/>
     </row>
     <row r="62" spans="4:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D62" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H62" s="110"/>
+      <c r="H62" s="106"/>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H63" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="I63" s="111"/>
+      <c r="H63" s="102" t="s">
+        <v>113</v>
+      </c>
+      <c r="I63" s="107"/>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D64" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H64" s="112" t="s">
-        <v>138</v>
-      </c>
-      <c r="I64" s="113">
+      <c r="H64" s="108" t="s">
+        <v>114</v>
+      </c>
+      <c r="I64" s="109">
         <f>I63*(1-I60)</f>
         <v>0</v>
       </c>
@@ -28787,10 +29111,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H65" s="108" t="s">
-        <v>139</v>
-      </c>
-      <c r="I65" s="114">
+      <c r="H65" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="I65" s="110">
         <f>I63*(1+I61)</f>
         <v>0</v>
       </c>
